--- a/data/output/delivery_export.xlsx
+++ b/data/output/delivery_export.xlsx
@@ -1679,7 +1679,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.bosch-home.com/us/en/product/SHPM65Z55N</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -2131,7 +2135,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.samsung.com/us/search/searchMain/?searchkeyword=DW80R9950US</t>
+          <t>https://www.samsung.com/us/home-appliances/dishwashers/all-dishwashers/DW80R9950US/</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -2583,7 +2587,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.geappliances.com/appliance/GE-Dishwasher-GDT695SSJSS</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -3029,7 +3037,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.mieleusa.com/e/G7316SCU</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -3479,7 +3491,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/us/dishwashers/lg-ldfn4542d/</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>

--- a/data/output/delivery_export.xlsx
+++ b/data/output/delivery_export.xlsx
@@ -1717,22 +1717,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>SHPM65Z55N Bosch 500 Series 24 Inch Built-In Dishwasher 44 dBA 120V 12A Stainless Steel</t>
+          <t>SHPM65Z55N Bosch 500 Series Dishwasher SS</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>-- Unbranded --</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>-- No Unilog Brand --</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>-- No DIB Brand --</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 12A 44DBA</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Bosch® Dishwasher, 500 Series, 120 V, 12 A, Built-in Mounting, 44 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+          <t>Bosch® Dishwasher, 500 Series, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1928,16 +1928,8 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>dBA</t>
-        </is>
-      </c>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
       <c r="CN2" t="inlineStr">
         <is>
           <t>Material</t>
@@ -2135,7 +2127,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.samsung.com/us/home-appliances/dishwashers/all-dishwashers/DW80R9950US/</t>
+          <t>https://www.samsung.com/us/support/model/DW80R9950US/AA/</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -2171,22 +2163,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>DW80R9950US Samsung Linear Wash 24 in Top Control Built In Dishwasher 39 dBA 120V 15A Stainless Steel</t>
+          <t>DW80R9950US Samsung Dishwasher SS - Display Only</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>-- Unbranded --</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>-- No Unilog Brand --</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>-- No DIB Brand --</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -2218,27 +2210,27 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Samsung, Dishwasher, Linear Wash, DW80R9950US, Built-in Mounting</t>
+          <t>Samsung, Dishwasher, Dishwasher, DW80R9950US, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A 39DBA</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Samsung® Linear Wash DW80R9950US Dishwasher, Built-in Mounting, Stainless Steel</t>
+          <t>Samsung® DW80R9950US Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Samsung® Dishwasher, Linear Wash, 120 V, 15 A, Built-in Mounting, 39 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+          <t>Samsung® Dishwasher, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Linear Wash Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -2281,11 +2273,7 @@
           <t>Series</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>Linear Wash</t>
-        </is>
-      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr">
         <is>
@@ -2382,16 +2370,8 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>dBA</t>
-        </is>
-      </c>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
       <c r="CN3" t="inlineStr">
         <is>
           <t>Material</t>
@@ -2587,11 +2567,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.geappliances.com/appliance/GE-Dishwasher-GDT695SSJSS</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -2625,37 +2601,37 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>GDT695SSJSS GE 24 Inch Built In Dishwasher 48 dBA 120V 15A Stainless Steel</t>
+          <t>GDT695SSJSS GE Dishwasher SS</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>GE Appliances</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>GE Appliances</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>GE</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Fastenal Company</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>GE Appliances</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>GE Appliances</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -2672,22 +2648,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>GE Appliances, Dishwasher, Dishwasher, GDT695SSJSS, Built-in Mounting</t>
+          <t>GE, Dishwasher, Dishwasher, GDT695SSJSS, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A 48DBA</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>GE Appliances® GDT695SSJSS Dishwasher, Built-in Mounting, Stainless Steel</t>
+          <t>GE® GDT695SSJSS Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GE Appliances® Dishwasher, 120 V, 15 A, Built-in Mounting, 48 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+          <t>GE® Dishwasher, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2832,16 +2808,8 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>dBA</t>
-        </is>
-      </c>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
       <c r="CN4" t="inlineStr">
         <is>
           <t>Material</t>
@@ -3037,11 +3005,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.mieleusa.com/e/G7316SCU</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -3075,27 +3039,27 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>G7316SCU Miele 24 Inch Built In Dishwasher AutoDos 42 dBA 120V 15A Clean Touch Steel</t>
+          <t>G7316SCU Miele Dishwasher SS</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Miele</t>
+          <t>-- Unbranded --</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Miele</t>
+          <t>-- No Unilog Brand --</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Miele</t>
+          <t>-- No DIB Brand --</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Grainger Industrial Supply</t>
+          <t>Freud Inc (2435)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -3122,27 +3086,27 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Miele, Dishwasher, Autodos, G7316SCU, Built-in Mounting</t>
+          <t>Miele, Dishwasher, Dishwasher, G7316SCU, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST 120V 15A 42DBA</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Miele® Autodos G7316SCU Dishwasher, Built-in Mounting, Stainless Steel, Clean Touch Steel</t>
+          <t>Miele® G7316SCU Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Miele® Dishwasher, Autodos, 120 V, 15 A, Built-in Mounting, 42 dBA Sound Level, Stainless Steel, Clean Touch Steel</t>
+          <t>Miele® Dishwasher, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Autodos Dishwasher, Built-in Mounting, Stainless Steel, Clean Touch Steel</t>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -3185,11 +3149,7 @@
           <t>Series</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>Autodos</t>
-        </is>
-      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr">
         <is>
@@ -3286,16 +3246,8 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>dBA</t>
-        </is>
-      </c>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
       <c r="CN5" t="inlineStr">
         <is>
           <t>Material</t>
@@ -3314,7 +3266,7 @@
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>Clean Touch Steel</t>
+          <t>Stainless Steel</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr"/>
@@ -3493,7 +3445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.lg.com/us/dishwashers/lg-ldfn4542d/</t>
+          <t>https://www.lg.com/us/support/product/lg-LDFN4542D</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -3529,27 +3481,27 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>LDFN4542D LG Front Control Dishwasher QuadWash 50 dBA 120V 15A Black Stainless Steel</t>
+          <t>LDFN4542D LG Dishwasher BSS</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>-- Unbranded --</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>-- No Unilog Brand --</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>-- No DIB Brand --</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>MSC Industrial Supply</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3576,27 +3528,27 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>LG, Dishwasher, Quadwash, LDFN4542D, Built-in Mounting</t>
+          <t>LG, Dishwasher, QuadWash Series, LDFN4542D, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A 50DBA</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>LG® Quadwash LDFN4542D Dishwasher, Built-in Mounting, Black Stainless Steel</t>
+          <t>LG® QuadWash Series LDFN4542D Dishwasher, Built-in Mounting, Black Stainless Steel</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>LG® Dishwasher, Quadwash, 120 V, 15 A, Built-in Mounting, 50 dBA Sound Level, Black Stainless Steel, Black Stainless Steel</t>
+          <t>LG® Dishwasher, QuadWash Series, 120 V, 15 A, Built-in Mounting, Black Stainless Steel, Black Stainless Steel</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Quadwash Dishwasher, Built-in Mounting, Black Stainless Steel, Black Stainless Steel</t>
+          <t>QuadWash Series Dishwasher, Built-in Mounting, Black Stainless Steel, Black Stainless Steel</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -3641,7 +3593,7 @@
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>Quadwash</t>
+          <t>QuadWash Series</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr"/>
@@ -3740,16 +3692,8 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>dBA</t>
-        </is>
-      </c>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
       <c r="CN6" t="inlineStr">
         <is>
           <t>Material</t>

--- a/data/output/delivery_export.xlsx
+++ b/data/output/delivery_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IR6"/>
+  <dimension ref="A1:IR16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,11 +1679,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.bosch-home.com/us/en/product/SHPM65Z55N</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -1712,12 +1708,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SHPM65Z55N</t>
+          <t>MDB8959SKZ</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>SHPM65Z55N Bosch 500 Series Dishwasher SS</t>
+          <t>MDB8959SKZ Maytag Top Control Dishwasher 47 dBA 120V 15A Stainless Steel</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1742,18 +1738,18 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>BSH Home Appliances</t>
+          <t>Whirlpool Corporation</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Maytag</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SHPM65Z55N</t>
+          <t>MDB8959SKZ</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -1764,27 +1760,27 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Bosch, Dishwasher, 500 Series, SHPM65Z55N, Built-in Mounting</t>
+          <t>Maytag, Dishwasher, MDB8959SKZ, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 47DBA</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Bosch® 500 Series SHPM65Z55N Dishwasher, Built-in Mounting, Stainless Steel</t>
+          <t>Maytag® MDB8959SKZ Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Bosch® Dishwasher, 500 Series, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>Maytag® Dishwasher, 120 V, 15 A, Built-in Mounting, 47 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>500 Series Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -1827,11 +1823,7 @@
           <t>Series</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>500 Series</t>
-        </is>
-      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr">
         <is>
@@ -1928,8 +1920,16 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
       <c r="CN2" t="inlineStr">
         <is>
           <t>Material</t>
@@ -2083,11 +2083,7 @@
       <c r="HN2" t="inlineStr"/>
       <c r="HO2" t="inlineStr"/>
       <c r="HP2" t="inlineStr"/>
-      <c r="HQ2" t="inlineStr">
-        <is>
-          <t>Bosch_SHPM65Z55N.jpg</t>
-        </is>
-      </c>
+      <c r="HQ2" t="inlineStr"/>
       <c r="HR2" t="inlineStr"/>
       <c r="HS2" t="inlineStr"/>
       <c r="HT2" t="inlineStr"/>
@@ -2096,11 +2092,7 @@
       <c r="HW2" t="inlineStr"/>
       <c r="HX2" t="inlineStr"/>
       <c r="HY2" t="inlineStr"/>
-      <c r="HZ2" t="inlineStr">
-        <is>
-          <t>Bosch_SHPM65Z55N_Specification_Sheet.pdf</t>
-        </is>
-      </c>
+      <c r="HZ2" t="inlineStr"/>
       <c r="IA2" t="inlineStr"/>
       <c r="IB2" t="inlineStr"/>
       <c r="IC2" t="inlineStr"/>
@@ -2120,16 +2112,12 @@
       <c r="IQ2" t="inlineStr"/>
       <c r="IR2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.samsung.com/us/support/model/DW80R9950US/AA/</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -2158,12 +2146,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DW80R9950US</t>
+          <t>DWHD650WFP</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>DW80R9950US Samsung Dishwasher SS - Display Only</t>
+          <t>DWHD650WFP Thermador Sapphire Series Dishwasher 40 dBA 120V 15A Panel Ready</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2183,23 +2171,23 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jam Industrial Supply LLC (JAMIN)</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>BSH Home Appliances</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Thermador</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>DW80R9950US</t>
+          <t>DWHD650WFP</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -2210,27 +2198,27 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Samsung, Dishwasher, Dishwasher, DW80R9950US, Built-in Mounting</t>
+          <t>Thermador, Dishwasher, DWHD650WFP, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
+          <t>DISHWASHER BLTLN PLS 120V 15A 40DBA</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Samsung® DW80R9950US Dishwasher, Built-in Mounting, Stainless Steel</t>
+          <t>Thermador® DWHD650WFP Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Samsung® Dishwasher, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>Thermador® Dishwasher, 120 V, 15 A, Built-in Mounting, 40 dBA Sound Level</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -2370,29 +2358,29 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
       <c r="CN3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>Stainless Steel</t>
-        </is>
-      </c>
+      <c r="CO3" t="inlineStr"/>
       <c r="CP3" t="inlineStr"/>
       <c r="CQ3" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>Stainless Steel</t>
-        </is>
-      </c>
+      <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="inlineStr"/>
       <c r="CT3" t="inlineStr">
         <is>
@@ -2525,11 +2513,7 @@
       <c r="HN3" t="inlineStr"/>
       <c r="HO3" t="inlineStr"/>
       <c r="HP3" t="inlineStr"/>
-      <c r="HQ3" t="inlineStr">
-        <is>
-          <t>Samsung_DW80R9950US.jpg</t>
-        </is>
-      </c>
+      <c r="HQ3" t="inlineStr"/>
       <c r="HR3" t="inlineStr"/>
       <c r="HS3" t="inlineStr"/>
       <c r="HT3" t="inlineStr"/>
@@ -2538,11 +2522,7 @@
       <c r="HW3" t="inlineStr"/>
       <c r="HX3" t="inlineStr"/>
       <c r="HY3" t="inlineStr"/>
-      <c r="HZ3" t="inlineStr">
-        <is>
-          <t>Samsung_DW80R9950US_Specification_Sheet.pdf</t>
-        </is>
-      </c>
+      <c r="HZ3" t="inlineStr"/>
       <c r="IA3" t="inlineStr"/>
       <c r="IB3" t="inlineStr"/>
       <c r="IC3" t="inlineStr"/>
@@ -2562,7 +2542,7 @@
       <c r="IQ3" t="inlineStr"/>
       <c r="IR3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2576,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>GDT695SSJSS</t>
+          <t>BDF450</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>GDT695SSJSS GE Dishwasher SS</t>
+          <t>BDF450 Beko Front Control Dishwasher 45 dBA 120V 12A Stainless Steel</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2621,23 +2601,23 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Appliance Dealers Cooperative (APPDE)</t>
+          <t>MSC Industrial Supply</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Arçelik</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>Beko</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>GDT695SSJSS</t>
+          <t>BDF450</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -2648,22 +2628,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>GE, Dishwasher, Dishwasher, GDT695SSJSS, Built-in Mounting</t>
+          <t>Beko, Dishwasher, BDF450, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
+          <t>DISHWASHER BLTLN SST SST 120V 12A 45DBA</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>GE® GDT695SSJSS Dishwasher, Built-in Mounting, Stainless Steel</t>
+          <t>Beko® BDF450 Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GE® Dishwasher, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>Beko® Dishwasher, 120 V, 12 A, Built-in Mounting, 45 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2749,7 +2729,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2808,8 +2788,16 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
       <c r="CN4" t="inlineStr">
         <is>
           <t>Material</t>
@@ -2963,11 +2951,7 @@
       <c r="HN4" t="inlineStr"/>
       <c r="HO4" t="inlineStr"/>
       <c r="HP4" t="inlineStr"/>
-      <c r="HQ4" t="inlineStr">
-        <is>
-          <t>GE_GDT695SSJSS.jpg</t>
-        </is>
-      </c>
+      <c r="HQ4" t="inlineStr"/>
       <c r="HR4" t="inlineStr"/>
       <c r="HS4" t="inlineStr"/>
       <c r="HT4" t="inlineStr"/>
@@ -2976,11 +2960,7 @@
       <c r="HW4" t="inlineStr"/>
       <c r="HX4" t="inlineStr"/>
       <c r="HY4" t="inlineStr"/>
-      <c r="HZ4" t="inlineStr">
-        <is>
-          <t>GE_GDT695SSJSS_Specification_Sheet.pdf</t>
-        </is>
-      </c>
+      <c r="HZ4" t="inlineStr"/>
       <c r="IA4" t="inlineStr"/>
       <c r="IB4" t="inlineStr"/>
       <c r="IC4" t="inlineStr"/>
@@ -3000,7 +2980,7 @@
       <c r="IQ4" t="inlineStr"/>
       <c r="IR4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,12 +3014,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>G7316SCU</t>
+          <t>DD24SDFT9N</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>G7316SCU Miele Dishwasher SS</t>
+          <t>DD24SDFT9N Fisher Paykel Double DishDrawer 44 dBA 120V 15A Stainless Steel</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -3059,23 +3039,23 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Freud Inc (2435)</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Miele Inc.</t>
+          <t>Fisher &amp; Paykel Appliances</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Miele</t>
+          <t>Fisher &amp; Paykel</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>G7316SCU</t>
+          <t>DD24SDFT9N</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -3086,22 +3066,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Miele, Dishwasher, Dishwasher, G7316SCU, Built-in Mounting</t>
+          <t>Fisher &amp; Paykel, Dishwasher, DD24SDFT9N, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 44DBA</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Miele® G7316SCU Dishwasher, Built-in Mounting, Stainless Steel</t>
+          <t>Fisher &amp; Paykel® DD24SDFT9N Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Miele® Dishwasher, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>Fisher &amp; Paykel® Dishwasher, 120 V, 15 A, Built-in Mounting, 44 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -3246,8 +3226,16 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
       <c r="CN5" t="inlineStr">
         <is>
           <t>Material</t>
@@ -3401,11 +3389,7 @@
       <c r="HN5" t="inlineStr"/>
       <c r="HO5" t="inlineStr"/>
       <c r="HP5" t="inlineStr"/>
-      <c r="HQ5" t="inlineStr">
-        <is>
-          <t>Miele_G7316SCU.jpg</t>
-        </is>
-      </c>
+      <c r="HQ5" t="inlineStr"/>
       <c r="HR5" t="inlineStr"/>
       <c r="HS5" t="inlineStr"/>
       <c r="HT5" t="inlineStr"/>
@@ -3414,11 +3398,7 @@
       <c r="HW5" t="inlineStr"/>
       <c r="HX5" t="inlineStr"/>
       <c r="HY5" t="inlineStr"/>
-      <c r="HZ5" t="inlineStr">
-        <is>
-          <t>Miele_G7316SCU_Specification_Sheet.pdf</t>
-        </is>
-      </c>
+      <c r="HZ5" t="inlineStr"/>
       <c r="IA5" t="inlineStr"/>
       <c r="IB5" t="inlineStr"/>
       <c r="IC5" t="inlineStr"/>
@@ -3438,16 +3418,12 @@
       <c r="IQ5" t="inlineStr"/>
       <c r="IR5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/us/support/product/lg-LDFN4542D</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -3476,12 +3452,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>LDFN4542D</t>
+          <t>WDT750SAKZ</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>LDFN4542D LG Dishwasher BSS</t>
+          <t>WDT750SAKZ Whirlpool Top Control Dishwasher 47 dBA 120V 15A Fingerprint Resistant</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -3506,18 +3482,18 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>Whirlpool Corporation</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Whirlpool®</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>LDFN4542D</t>
+          <t>WDT750SAKZ</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -3528,27 +3504,27 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>LG, Dishwasher, QuadWash Series, LDFN4542D, Built-in Mounting</t>
+          <t>Whirlpool, Dishwasher, Eco Series, WDT750SAKZ, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
+          <t>DISHWASHER BLTLN PLS 120V 15A 47DBA</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>LG® QuadWash Series LDFN4542D Dishwasher, Built-in Mounting, Black Stainless Steel</t>
+          <t>Whirlpool® Eco Series WDT750SAKZ Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>LG® Dishwasher, QuadWash Series, 120 V, 15 A, Built-in Mounting, Black Stainless Steel, Black Stainless Steel</t>
+          <t>Whirlpool® Dishwasher, Eco Series, 120 V, 15 A, Built-in Mounting, 47 dBA Sound Level</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>QuadWash Series Dishwasher, Built-in Mounting, Black Stainless Steel, Black Stainless Steel</t>
+          <t>Eco Series Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -3593,7 +3569,7 @@
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>QuadWash Series</t>
+          <t>Eco Series</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr"/>
@@ -3692,29 +3668,29 @@
           <t>Sound Level</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
       <c r="CN6" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>Black Stainless Steel</t>
-        </is>
-      </c>
+      <c r="CO6" t="inlineStr"/>
       <c r="CP6" t="inlineStr"/>
       <c r="CQ6" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>Black Stainless Steel</t>
-        </is>
-      </c>
+      <c r="CR6" t="inlineStr"/>
       <c r="CS6" t="inlineStr"/>
       <c r="CT6" t="inlineStr">
         <is>
@@ -3847,11 +3823,7 @@
       <c r="HN6" t="inlineStr"/>
       <c r="HO6" t="inlineStr"/>
       <c r="HP6" t="inlineStr"/>
-      <c r="HQ6" t="inlineStr">
-        <is>
-          <t>LG_LDFN4542D.jpg</t>
-        </is>
-      </c>
+      <c r="HQ6" t="inlineStr"/>
       <c r="HR6" t="inlineStr"/>
       <c r="HS6" t="inlineStr"/>
       <c r="HT6" t="inlineStr"/>
@@ -3860,11 +3832,7 @@
       <c r="HW6" t="inlineStr"/>
       <c r="HX6" t="inlineStr"/>
       <c r="HY6" t="inlineStr"/>
-      <c r="HZ6" t="inlineStr">
-        <is>
-          <t>LG_LDFN4542D_Specification_Sheet.pdf</t>
-        </is>
-      </c>
+      <c r="HZ6" t="inlineStr"/>
       <c r="IA6" t="inlineStr"/>
       <c r="IB6" t="inlineStr"/>
       <c r="IC6" t="inlineStr"/>
@@ -3884,7 +3852,4399 @@
       <c r="IQ6" t="inlineStr"/>
       <c r="IR6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1515805</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>KDTM404KPS</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>KDTM404KPS KitchenAid 44 dBA Dishwasher PrintShield Stainless Steel</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Whirlpool Corporation</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>KitchenAid</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>KDTM404KPS</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>KitchenAid, Dishwasher, PrintShield Series, KDTM404KPS, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 44DBA</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>KitchenAid® PrintShield Series KDTM404KPS Dishwasher, Built-in Mounting, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>KitchenAid® Dishwasher, PrintShield Series, 120 V, 15 A, Built-in Mounting, 44 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>PrintShield Series Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>PrintShield Series</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="inlineStr"/>
+      <c r="DM7" t="inlineStr"/>
+      <c r="DN7" t="inlineStr"/>
+      <c r="DO7" t="inlineStr"/>
+      <c r="DP7" t="inlineStr"/>
+      <c r="DQ7" t="inlineStr"/>
+      <c r="DR7" t="inlineStr"/>
+      <c r="DS7" t="inlineStr"/>
+      <c r="DT7" t="inlineStr"/>
+      <c r="DU7" t="inlineStr"/>
+      <c r="DV7" t="inlineStr"/>
+      <c r="DW7" t="inlineStr"/>
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr"/>
+      <c r="DZ7" t="inlineStr"/>
+      <c r="EA7" t="inlineStr"/>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr"/>
+      <c r="EE7" t="inlineStr"/>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
+      <c r="EK7" t="inlineStr"/>
+      <c r="EL7" t="inlineStr"/>
+      <c r="EM7" t="inlineStr"/>
+      <c r="EN7" t="inlineStr"/>
+      <c r="EO7" t="inlineStr"/>
+      <c r="EP7" t="inlineStr"/>
+      <c r="EQ7" t="inlineStr"/>
+      <c r="ER7" t="inlineStr"/>
+      <c r="ES7" t="inlineStr"/>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
+      <c r="EV7" t="inlineStr"/>
+      <c r="EW7" t="inlineStr"/>
+      <c r="EX7" t="inlineStr"/>
+      <c r="EY7" t="inlineStr"/>
+      <c r="EZ7" t="inlineStr"/>
+      <c r="FA7" t="inlineStr"/>
+      <c r="FB7" t="inlineStr"/>
+      <c r="FC7" t="inlineStr"/>
+      <c r="FD7" t="inlineStr"/>
+      <c r="FE7" t="inlineStr"/>
+      <c r="FF7" t="inlineStr"/>
+      <c r="FG7" t="inlineStr"/>
+      <c r="FH7" t="inlineStr"/>
+      <c r="FI7" t="inlineStr"/>
+      <c r="FJ7" t="inlineStr"/>
+      <c r="FK7" t="inlineStr"/>
+      <c r="FL7" t="inlineStr"/>
+      <c r="FM7" t="inlineStr"/>
+      <c r="FN7" t="inlineStr"/>
+      <c r="FO7" t="inlineStr"/>
+      <c r="FP7" t="inlineStr"/>
+      <c r="FQ7" t="inlineStr"/>
+      <c r="FR7" t="inlineStr"/>
+      <c r="FS7" t="inlineStr"/>
+      <c r="FT7" t="inlineStr"/>
+      <c r="FU7" t="inlineStr"/>
+      <c r="FV7" t="inlineStr"/>
+      <c r="FW7" t="inlineStr"/>
+      <c r="FX7" t="inlineStr"/>
+      <c r="FY7" t="inlineStr"/>
+      <c r="FZ7" t="inlineStr"/>
+      <c r="GA7" t="inlineStr"/>
+      <c r="GB7" t="inlineStr"/>
+      <c r="GC7" t="inlineStr"/>
+      <c r="GD7" t="inlineStr"/>
+      <c r="GE7" t="inlineStr"/>
+      <c r="GF7" t="inlineStr"/>
+      <c r="GG7" t="inlineStr"/>
+      <c r="GH7" t="inlineStr"/>
+      <c r="GI7" t="inlineStr"/>
+      <c r="GJ7" t="inlineStr"/>
+      <c r="GK7" t="inlineStr"/>
+      <c r="GL7" t="inlineStr"/>
+      <c r="GM7" t="inlineStr"/>
+      <c r="GN7" t="inlineStr"/>
+      <c r="GO7" t="inlineStr"/>
+      <c r="GP7" t="inlineStr"/>
+      <c r="GQ7" t="inlineStr"/>
+      <c r="GR7" t="inlineStr"/>
+      <c r="GS7" t="inlineStr"/>
+      <c r="GT7" t="inlineStr"/>
+      <c r="GU7" t="inlineStr"/>
+      <c r="GV7" t="inlineStr"/>
+      <c r="GW7" t="inlineStr"/>
+      <c r="GX7" t="inlineStr"/>
+      <c r="GY7" t="inlineStr"/>
+      <c r="GZ7" t="inlineStr"/>
+      <c r="HA7" t="inlineStr"/>
+      <c r="HB7" t="inlineStr"/>
+      <c r="HC7" t="inlineStr"/>
+      <c r="HD7" t="inlineStr"/>
+      <c r="HE7" t="inlineStr"/>
+      <c r="HF7" t="inlineStr"/>
+      <c r="HG7" t="inlineStr"/>
+      <c r="HH7" t="inlineStr"/>
+      <c r="HI7" t="inlineStr"/>
+      <c r="HJ7" t="inlineStr"/>
+      <c r="HK7" t="inlineStr"/>
+      <c r="HL7" t="inlineStr"/>
+      <c r="HM7" t="inlineStr"/>
+      <c r="HN7" t="inlineStr"/>
+      <c r="HO7" t="inlineStr"/>
+      <c r="HP7" t="inlineStr"/>
+      <c r="HQ7" t="inlineStr"/>
+      <c r="HR7" t="inlineStr"/>
+      <c r="HS7" t="inlineStr"/>
+      <c r="HT7" t="inlineStr"/>
+      <c r="HU7" t="inlineStr"/>
+      <c r="HV7" t="inlineStr"/>
+      <c r="HW7" t="inlineStr"/>
+      <c r="HX7" t="inlineStr"/>
+      <c r="HY7" t="inlineStr"/>
+      <c r="HZ7" t="inlineStr"/>
+      <c r="IA7" t="inlineStr"/>
+      <c r="IB7" t="inlineStr"/>
+      <c r="IC7" t="inlineStr"/>
+      <c r="ID7" t="inlineStr"/>
+      <c r="IE7" t="inlineStr"/>
+      <c r="IF7" t="inlineStr"/>
+      <c r="IG7" t="inlineStr"/>
+      <c r="IH7" t="inlineStr"/>
+      <c r="II7" t="inlineStr"/>
+      <c r="IJ7" t="inlineStr"/>
+      <c r="IK7" t="inlineStr"/>
+      <c r="IL7" t="inlineStr"/>
+      <c r="IM7" t="inlineStr"/>
+      <c r="IN7" t="inlineStr"/>
+      <c r="IO7" t="inlineStr"/>
+      <c r="IP7" t="inlineStr"/>
+      <c r="IQ7" t="inlineStr"/>
+      <c r="IR7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1515806</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>GDF650SSVSS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>GDF650SSVSS GE Front Control Dishwasher 51 dBA 120V 15A Stainless Steel</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Grainger Industrial Supply</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>GE Appliances</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>GDF650SSVSS</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>GE, Dishwasher, GDF650SSVSS, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 51DBA</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>GE® GDF650SSVSS Dishwasher, Built-in Mounting, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>GE® Dishwasher, 120 V, 15 A, Built-in Mounting, 51 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="inlineStr"/>
+      <c r="DM8" t="inlineStr"/>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr"/>
+      <c r="DP8" t="inlineStr"/>
+      <c r="DQ8" t="inlineStr"/>
+      <c r="DR8" t="inlineStr"/>
+      <c r="DS8" t="inlineStr"/>
+      <c r="DT8" t="inlineStr"/>
+      <c r="DU8" t="inlineStr"/>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr"/>
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr"/>
+      <c r="DZ8" t="inlineStr"/>
+      <c r="EA8" t="inlineStr"/>
+      <c r="EB8" t="inlineStr"/>
+      <c r="EC8" t="inlineStr"/>
+      <c r="ED8" t="inlineStr"/>
+      <c r="EE8" t="inlineStr"/>
+      <c r="EF8" t="inlineStr"/>
+      <c r="EG8" t="inlineStr"/>
+      <c r="EH8" t="inlineStr"/>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr"/>
+      <c r="EL8" t="inlineStr"/>
+      <c r="EM8" t="inlineStr"/>
+      <c r="EN8" t="inlineStr"/>
+      <c r="EO8" t="inlineStr"/>
+      <c r="EP8" t="inlineStr"/>
+      <c r="EQ8" t="inlineStr"/>
+      <c r="ER8" t="inlineStr"/>
+      <c r="ES8" t="inlineStr"/>
+      <c r="ET8" t="inlineStr"/>
+      <c r="EU8" t="inlineStr"/>
+      <c r="EV8" t="inlineStr"/>
+      <c r="EW8" t="inlineStr"/>
+      <c r="EX8" t="inlineStr"/>
+      <c r="EY8" t="inlineStr"/>
+      <c r="EZ8" t="inlineStr"/>
+      <c r="FA8" t="inlineStr"/>
+      <c r="FB8" t="inlineStr"/>
+      <c r="FC8" t="inlineStr"/>
+      <c r="FD8" t="inlineStr"/>
+      <c r="FE8" t="inlineStr"/>
+      <c r="FF8" t="inlineStr"/>
+      <c r="FG8" t="inlineStr"/>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+      <c r="FL8" t="inlineStr"/>
+      <c r="FM8" t="inlineStr"/>
+      <c r="FN8" t="inlineStr"/>
+      <c r="FO8" t="inlineStr"/>
+      <c r="FP8" t="inlineStr"/>
+      <c r="FQ8" t="inlineStr"/>
+      <c r="FR8" t="inlineStr"/>
+      <c r="FS8" t="inlineStr"/>
+      <c r="FT8" t="inlineStr"/>
+      <c r="FU8" t="inlineStr"/>
+      <c r="FV8" t="inlineStr"/>
+      <c r="FW8" t="inlineStr"/>
+      <c r="FX8" t="inlineStr"/>
+      <c r="FY8" t="inlineStr"/>
+      <c r="FZ8" t="inlineStr"/>
+      <c r="GA8" t="inlineStr"/>
+      <c r="GB8" t="inlineStr"/>
+      <c r="GC8" t="inlineStr"/>
+      <c r="GD8" t="inlineStr"/>
+      <c r="GE8" t="inlineStr"/>
+      <c r="GF8" t="inlineStr"/>
+      <c r="GG8" t="inlineStr"/>
+      <c r="GH8" t="inlineStr"/>
+      <c r="GI8" t="inlineStr"/>
+      <c r="GJ8" t="inlineStr"/>
+      <c r="GK8" t="inlineStr"/>
+      <c r="GL8" t="inlineStr"/>
+      <c r="GM8" t="inlineStr"/>
+      <c r="GN8" t="inlineStr"/>
+      <c r="GO8" t="inlineStr"/>
+      <c r="GP8" t="inlineStr"/>
+      <c r="GQ8" t="inlineStr"/>
+      <c r="GR8" t="inlineStr"/>
+      <c r="GS8" t="inlineStr"/>
+      <c r="GT8" t="inlineStr"/>
+      <c r="GU8" t="inlineStr"/>
+      <c r="GV8" t="inlineStr"/>
+      <c r="GW8" t="inlineStr"/>
+      <c r="GX8" t="inlineStr"/>
+      <c r="GY8" t="inlineStr"/>
+      <c r="GZ8" t="inlineStr"/>
+      <c r="HA8" t="inlineStr"/>
+      <c r="HB8" t="inlineStr"/>
+      <c r="HC8" t="inlineStr"/>
+      <c r="HD8" t="inlineStr"/>
+      <c r="HE8" t="inlineStr"/>
+      <c r="HF8" t="inlineStr"/>
+      <c r="HG8" t="inlineStr"/>
+      <c r="HH8" t="inlineStr"/>
+      <c r="HI8" t="inlineStr"/>
+      <c r="HJ8" t="inlineStr"/>
+      <c r="HK8" t="inlineStr"/>
+      <c r="HL8" t="inlineStr"/>
+      <c r="HM8" t="inlineStr"/>
+      <c r="HN8" t="inlineStr"/>
+      <c r="HO8" t="inlineStr"/>
+      <c r="HP8" t="inlineStr"/>
+      <c r="HQ8" t="inlineStr"/>
+      <c r="HR8" t="inlineStr"/>
+      <c r="HS8" t="inlineStr"/>
+      <c r="HT8" t="inlineStr"/>
+      <c r="HU8" t="inlineStr"/>
+      <c r="HV8" t="inlineStr"/>
+      <c r="HW8" t="inlineStr"/>
+      <c r="HX8" t="inlineStr"/>
+      <c r="HY8" t="inlineStr"/>
+      <c r="HZ8" t="inlineStr"/>
+      <c r="IA8" t="inlineStr"/>
+      <c r="IB8" t="inlineStr"/>
+      <c r="IC8" t="inlineStr"/>
+      <c r="ID8" t="inlineStr"/>
+      <c r="IE8" t="inlineStr"/>
+      <c r="IF8" t="inlineStr"/>
+      <c r="IG8" t="inlineStr"/>
+      <c r="IH8" t="inlineStr"/>
+      <c r="II8" t="inlineStr"/>
+      <c r="IJ8" t="inlineStr"/>
+      <c r="IK8" t="inlineStr"/>
+      <c r="IL8" t="inlineStr"/>
+      <c r="IM8" t="inlineStr"/>
+      <c r="IN8" t="inlineStr"/>
+      <c r="IO8" t="inlineStr"/>
+      <c r="IP8" t="inlineStr"/>
+      <c r="IQ8" t="inlineStr"/>
+      <c r="IR8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1515807</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>FFID2426TS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FFID2426TS Frigidaire Built-In Dishwasher 54 dBA 120V 15A Stainless Steel</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Freud Inc (2435)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Rheem Manufacturing</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>FRIGIDAIRE®</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>FFID2426TS</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Rheem Manufacturing FRIGIDAIRE, Dishwasher, Professional Series, FFID2426TS, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 54DBA</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>FRIGIDAIRE® Professional Series FFID2426TS Dishwasher, Built-in Mounting, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>FRIGIDAIRE® Dishwasher, Professional Series, 120 V, 15 A, Built-in Mounting, 54 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Professional Series Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>Professional Series</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="inlineStr"/>
+      <c r="DM9" t="inlineStr"/>
+      <c r="DN9" t="inlineStr"/>
+      <c r="DO9" t="inlineStr"/>
+      <c r="DP9" t="inlineStr"/>
+      <c r="DQ9" t="inlineStr"/>
+      <c r="DR9" t="inlineStr"/>
+      <c r="DS9" t="inlineStr"/>
+      <c r="DT9" t="inlineStr"/>
+      <c r="DU9" t="inlineStr"/>
+      <c r="DV9" t="inlineStr"/>
+      <c r="DW9" t="inlineStr"/>
+      <c r="DX9" t="inlineStr"/>
+      <c r="DY9" t="inlineStr"/>
+      <c r="DZ9" t="inlineStr"/>
+      <c r="EA9" t="inlineStr"/>
+      <c r="EB9" t="inlineStr"/>
+      <c r="EC9" t="inlineStr"/>
+      <c r="ED9" t="inlineStr"/>
+      <c r="EE9" t="inlineStr"/>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
+      <c r="EM9" t="inlineStr"/>
+      <c r="EN9" t="inlineStr"/>
+      <c r="EO9" t="inlineStr"/>
+      <c r="EP9" t="inlineStr"/>
+      <c r="EQ9" t="inlineStr"/>
+      <c r="ER9" t="inlineStr"/>
+      <c r="ES9" t="inlineStr"/>
+      <c r="ET9" t="inlineStr"/>
+      <c r="EU9" t="inlineStr"/>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
+      <c r="EX9" t="inlineStr"/>
+      <c r="EY9" t="inlineStr"/>
+      <c r="EZ9" t="inlineStr"/>
+      <c r="FA9" t="inlineStr"/>
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr"/>
+      <c r="FE9" t="inlineStr"/>
+      <c r="FF9" t="inlineStr"/>
+      <c r="FG9" t="inlineStr"/>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="inlineStr"/>
+      <c r="FN9" t="inlineStr"/>
+      <c r="FO9" t="inlineStr"/>
+      <c r="FP9" t="inlineStr"/>
+      <c r="FQ9" t="inlineStr"/>
+      <c r="FR9" t="inlineStr"/>
+      <c r="FS9" t="inlineStr"/>
+      <c r="FT9" t="inlineStr"/>
+      <c r="FU9" t="inlineStr"/>
+      <c r="FV9" t="inlineStr"/>
+      <c r="FW9" t="inlineStr"/>
+      <c r="FX9" t="inlineStr"/>
+      <c r="FY9" t="inlineStr"/>
+      <c r="FZ9" t="inlineStr"/>
+      <c r="GA9" t="inlineStr"/>
+      <c r="GB9" t="inlineStr"/>
+      <c r="GC9" t="inlineStr"/>
+      <c r="GD9" t="inlineStr"/>
+      <c r="GE9" t="inlineStr"/>
+      <c r="GF9" t="inlineStr"/>
+      <c r="GG9" t="inlineStr"/>
+      <c r="GH9" t="inlineStr"/>
+      <c r="GI9" t="inlineStr"/>
+      <c r="GJ9" t="inlineStr"/>
+      <c r="GK9" t="inlineStr"/>
+      <c r="GL9" t="inlineStr"/>
+      <c r="GM9" t="inlineStr"/>
+      <c r="GN9" t="inlineStr"/>
+      <c r="GO9" t="inlineStr"/>
+      <c r="GP9" t="inlineStr"/>
+      <c r="GQ9" t="inlineStr"/>
+      <c r="GR9" t="inlineStr"/>
+      <c r="GS9" t="inlineStr"/>
+      <c r="GT9" t="inlineStr"/>
+      <c r="GU9" t="inlineStr"/>
+      <c r="GV9" t="inlineStr"/>
+      <c r="GW9" t="inlineStr"/>
+      <c r="GX9" t="inlineStr"/>
+      <c r="GY9" t="inlineStr"/>
+      <c r="GZ9" t="inlineStr"/>
+      <c r="HA9" t="inlineStr"/>
+      <c r="HB9" t="inlineStr"/>
+      <c r="HC9" t="inlineStr"/>
+      <c r="HD9" t="inlineStr"/>
+      <c r="HE9" t="inlineStr"/>
+      <c r="HF9" t="inlineStr"/>
+      <c r="HG9" t="inlineStr"/>
+      <c r="HH9" t="inlineStr"/>
+      <c r="HI9" t="inlineStr"/>
+      <c r="HJ9" t="inlineStr"/>
+      <c r="HK9" t="inlineStr"/>
+      <c r="HL9" t="inlineStr"/>
+      <c r="HM9" t="inlineStr"/>
+      <c r="HN9" t="inlineStr"/>
+      <c r="HO9" t="inlineStr"/>
+      <c r="HP9" t="inlineStr"/>
+      <c r="HQ9" t="inlineStr"/>
+      <c r="HR9" t="inlineStr"/>
+      <c r="HS9" t="inlineStr"/>
+      <c r="HT9" t="inlineStr"/>
+      <c r="HU9" t="inlineStr"/>
+      <c r="HV9" t="inlineStr"/>
+      <c r="HW9" t="inlineStr"/>
+      <c r="HX9" t="inlineStr"/>
+      <c r="HY9" t="inlineStr"/>
+      <c r="HZ9" t="inlineStr"/>
+      <c r="IA9" t="inlineStr"/>
+      <c r="IB9" t="inlineStr"/>
+      <c r="IC9" t="inlineStr"/>
+      <c r="ID9" t="inlineStr"/>
+      <c r="IE9" t="inlineStr"/>
+      <c r="IF9" t="inlineStr"/>
+      <c r="IG9" t="inlineStr"/>
+      <c r="IH9" t="inlineStr"/>
+      <c r="II9" t="inlineStr"/>
+      <c r="IJ9" t="inlineStr"/>
+      <c r="IK9" t="inlineStr"/>
+      <c r="IL9" t="inlineStr"/>
+      <c r="IM9" t="inlineStr"/>
+      <c r="IN9" t="inlineStr"/>
+      <c r="IO9" t="inlineStr"/>
+      <c r="IP9" t="inlineStr"/>
+      <c r="IQ9" t="inlineStr"/>
+      <c r="IR9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.samsung.com/us/support/model/DW80CG5450SR/AA/</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1515808</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DW80CG5450SR</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DW80CG5450SR Samsung StormWash Dishwasher 42 dBA 120V 15A Stainless Steel</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>DW80CG5450SR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Samsung, Dishwasher, DW80CG5450SR, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 42DBA</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Samsung® DW80CG5450SR Dishwasher, Built-in Mounting, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Samsung® Dishwasher, 120 V, 15 A, Built-in Mounting, 42 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="inlineStr"/>
+      <c r="DM10" t="inlineStr"/>
+      <c r="DN10" t="inlineStr"/>
+      <c r="DO10" t="inlineStr"/>
+      <c r="DP10" t="inlineStr"/>
+      <c r="DQ10" t="inlineStr"/>
+      <c r="DR10" t="inlineStr"/>
+      <c r="DS10" t="inlineStr"/>
+      <c r="DT10" t="inlineStr"/>
+      <c r="DU10" t="inlineStr"/>
+      <c r="DV10" t="inlineStr"/>
+      <c r="DW10" t="inlineStr"/>
+      <c r="DX10" t="inlineStr"/>
+      <c r="DY10" t="inlineStr"/>
+      <c r="DZ10" t="inlineStr"/>
+      <c r="EA10" t="inlineStr"/>
+      <c r="EB10" t="inlineStr"/>
+      <c r="EC10" t="inlineStr"/>
+      <c r="ED10" t="inlineStr"/>
+      <c r="EE10" t="inlineStr"/>
+      <c r="EF10" t="inlineStr"/>
+      <c r="EG10" t="inlineStr"/>
+      <c r="EH10" t="inlineStr"/>
+      <c r="EI10" t="inlineStr"/>
+      <c r="EJ10" t="inlineStr"/>
+      <c r="EK10" t="inlineStr"/>
+      <c r="EL10" t="inlineStr"/>
+      <c r="EM10" t="inlineStr"/>
+      <c r="EN10" t="inlineStr"/>
+      <c r="EO10" t="inlineStr"/>
+      <c r="EP10" t="inlineStr"/>
+      <c r="EQ10" t="inlineStr"/>
+      <c r="ER10" t="inlineStr"/>
+      <c r="ES10" t="inlineStr"/>
+      <c r="ET10" t="inlineStr"/>
+      <c r="EU10" t="inlineStr"/>
+      <c r="EV10" t="inlineStr"/>
+      <c r="EW10" t="inlineStr"/>
+      <c r="EX10" t="inlineStr"/>
+      <c r="EY10" t="inlineStr"/>
+      <c r="EZ10" t="inlineStr"/>
+      <c r="FA10" t="inlineStr"/>
+      <c r="FB10" t="inlineStr"/>
+      <c r="FC10" t="inlineStr"/>
+      <c r="FD10" t="inlineStr"/>
+      <c r="FE10" t="inlineStr"/>
+      <c r="FF10" t="inlineStr"/>
+      <c r="FG10" t="inlineStr"/>
+      <c r="FH10" t="inlineStr"/>
+      <c r="FI10" t="inlineStr"/>
+      <c r="FJ10" t="inlineStr"/>
+      <c r="FK10" t="inlineStr"/>
+      <c r="FL10" t="inlineStr"/>
+      <c r="FM10" t="inlineStr"/>
+      <c r="FN10" t="inlineStr"/>
+      <c r="FO10" t="inlineStr"/>
+      <c r="FP10" t="inlineStr"/>
+      <c r="FQ10" t="inlineStr"/>
+      <c r="FR10" t="inlineStr"/>
+      <c r="FS10" t="inlineStr"/>
+      <c r="FT10" t="inlineStr"/>
+      <c r="FU10" t="inlineStr"/>
+      <c r="FV10" t="inlineStr"/>
+      <c r="FW10" t="inlineStr"/>
+      <c r="FX10" t="inlineStr"/>
+      <c r="FY10" t="inlineStr"/>
+      <c r="FZ10" t="inlineStr"/>
+      <c r="GA10" t="inlineStr"/>
+      <c r="GB10" t="inlineStr"/>
+      <c r="GC10" t="inlineStr"/>
+      <c r="GD10" t="inlineStr"/>
+      <c r="GE10" t="inlineStr"/>
+      <c r="GF10" t="inlineStr"/>
+      <c r="GG10" t="inlineStr"/>
+      <c r="GH10" t="inlineStr"/>
+      <c r="GI10" t="inlineStr"/>
+      <c r="GJ10" t="inlineStr"/>
+      <c r="GK10" t="inlineStr"/>
+      <c r="GL10" t="inlineStr"/>
+      <c r="GM10" t="inlineStr"/>
+      <c r="GN10" t="inlineStr"/>
+      <c r="GO10" t="inlineStr"/>
+      <c r="GP10" t="inlineStr"/>
+      <c r="GQ10" t="inlineStr"/>
+      <c r="GR10" t="inlineStr"/>
+      <c r="GS10" t="inlineStr"/>
+      <c r="GT10" t="inlineStr"/>
+      <c r="GU10" t="inlineStr"/>
+      <c r="GV10" t="inlineStr"/>
+      <c r="GW10" t="inlineStr"/>
+      <c r="GX10" t="inlineStr"/>
+      <c r="GY10" t="inlineStr"/>
+      <c r="GZ10" t="inlineStr"/>
+      <c r="HA10" t="inlineStr"/>
+      <c r="HB10" t="inlineStr"/>
+      <c r="HC10" t="inlineStr"/>
+      <c r="HD10" t="inlineStr"/>
+      <c r="HE10" t="inlineStr"/>
+      <c r="HF10" t="inlineStr"/>
+      <c r="HG10" t="inlineStr"/>
+      <c r="HH10" t="inlineStr"/>
+      <c r="HI10" t="inlineStr"/>
+      <c r="HJ10" t="inlineStr"/>
+      <c r="HK10" t="inlineStr"/>
+      <c r="HL10" t="inlineStr"/>
+      <c r="HM10" t="inlineStr"/>
+      <c r="HN10" t="inlineStr"/>
+      <c r="HO10" t="inlineStr"/>
+      <c r="HP10" t="inlineStr"/>
+      <c r="HQ10" t="inlineStr"/>
+      <c r="HR10" t="inlineStr"/>
+      <c r="HS10" t="inlineStr"/>
+      <c r="HT10" t="inlineStr"/>
+      <c r="HU10" t="inlineStr"/>
+      <c r="HV10" t="inlineStr"/>
+      <c r="HW10" t="inlineStr"/>
+      <c r="HX10" t="inlineStr"/>
+      <c r="HY10" t="inlineStr"/>
+      <c r="HZ10" t="inlineStr"/>
+      <c r="IA10" t="inlineStr"/>
+      <c r="IB10" t="inlineStr"/>
+      <c r="IC10" t="inlineStr"/>
+      <c r="ID10" t="inlineStr"/>
+      <c r="IE10" t="inlineStr"/>
+      <c r="IF10" t="inlineStr"/>
+      <c r="IG10" t="inlineStr"/>
+      <c r="IH10" t="inlineStr"/>
+      <c r="II10" t="inlineStr"/>
+      <c r="IJ10" t="inlineStr"/>
+      <c r="IK10" t="inlineStr"/>
+      <c r="IL10" t="inlineStr"/>
+      <c r="IM10" t="inlineStr"/>
+      <c r="IN10" t="inlineStr"/>
+      <c r="IO10" t="inlineStr"/>
+      <c r="IP10" t="inlineStr"/>
+      <c r="IQ10" t="inlineStr"/>
+      <c r="IR10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1515809</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>LDTS5551D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>LDTS5551D LG Top Control Dishwasher QuadWash 46 dBA 120V 15A Stainless Steel</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>MSC Industrial Supply</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LG Electronics</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>LDTS5551D</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>LG, Dishwasher, Quadwash, LDTS5551D, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 46DBA</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>LG® Quadwash LDTS5551D Dishwasher, Built-in Mounting, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>LG® Dishwasher, Quadwash, 120 V, 15 A, Built-in Mounting, 46 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Quadwash Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>Quadwash</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr"/>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="inlineStr"/>
+      <c r="DJ11" t="inlineStr"/>
+      <c r="DK11" t="inlineStr"/>
+      <c r="DL11" t="inlineStr"/>
+      <c r="DM11" t="inlineStr"/>
+      <c r="DN11" t="inlineStr"/>
+      <c r="DO11" t="inlineStr"/>
+      <c r="DP11" t="inlineStr"/>
+      <c r="DQ11" t="inlineStr"/>
+      <c r="DR11" t="inlineStr"/>
+      <c r="DS11" t="inlineStr"/>
+      <c r="DT11" t="inlineStr"/>
+      <c r="DU11" t="inlineStr"/>
+      <c r="DV11" t="inlineStr"/>
+      <c r="DW11" t="inlineStr"/>
+      <c r="DX11" t="inlineStr"/>
+      <c r="DY11" t="inlineStr"/>
+      <c r="DZ11" t="inlineStr"/>
+      <c r="EA11" t="inlineStr"/>
+      <c r="EB11" t="inlineStr"/>
+      <c r="EC11" t="inlineStr"/>
+      <c r="ED11" t="inlineStr"/>
+      <c r="EE11" t="inlineStr"/>
+      <c r="EF11" t="inlineStr"/>
+      <c r="EG11" t="inlineStr"/>
+      <c r="EH11" t="inlineStr"/>
+      <c r="EI11" t="inlineStr"/>
+      <c r="EJ11" t="inlineStr"/>
+      <c r="EK11" t="inlineStr"/>
+      <c r="EL11" t="inlineStr"/>
+      <c r="EM11" t="inlineStr"/>
+      <c r="EN11" t="inlineStr"/>
+      <c r="EO11" t="inlineStr"/>
+      <c r="EP11" t="inlineStr"/>
+      <c r="EQ11" t="inlineStr"/>
+      <c r="ER11" t="inlineStr"/>
+      <c r="ES11" t="inlineStr"/>
+      <c r="ET11" t="inlineStr"/>
+      <c r="EU11" t="inlineStr"/>
+      <c r="EV11" t="inlineStr"/>
+      <c r="EW11" t="inlineStr"/>
+      <c r="EX11" t="inlineStr"/>
+      <c r="EY11" t="inlineStr"/>
+      <c r="EZ11" t="inlineStr"/>
+      <c r="FA11" t="inlineStr"/>
+      <c r="FB11" t="inlineStr"/>
+      <c r="FC11" t="inlineStr"/>
+      <c r="FD11" t="inlineStr"/>
+      <c r="FE11" t="inlineStr"/>
+      <c r="FF11" t="inlineStr"/>
+      <c r="FG11" t="inlineStr"/>
+      <c r="FH11" t="inlineStr"/>
+      <c r="FI11" t="inlineStr"/>
+      <c r="FJ11" t="inlineStr"/>
+      <c r="FK11" t="inlineStr"/>
+      <c r="FL11" t="inlineStr"/>
+      <c r="FM11" t="inlineStr"/>
+      <c r="FN11" t="inlineStr"/>
+      <c r="FO11" t="inlineStr"/>
+      <c r="FP11" t="inlineStr"/>
+      <c r="FQ11" t="inlineStr"/>
+      <c r="FR11" t="inlineStr"/>
+      <c r="FS11" t="inlineStr"/>
+      <c r="FT11" t="inlineStr"/>
+      <c r="FU11" t="inlineStr"/>
+      <c r="FV11" t="inlineStr"/>
+      <c r="FW11" t="inlineStr"/>
+      <c r="FX11" t="inlineStr"/>
+      <c r="FY11" t="inlineStr"/>
+      <c r="FZ11" t="inlineStr"/>
+      <c r="GA11" t="inlineStr"/>
+      <c r="GB11" t="inlineStr"/>
+      <c r="GC11" t="inlineStr"/>
+      <c r="GD11" t="inlineStr"/>
+      <c r="GE11" t="inlineStr"/>
+      <c r="GF11" t="inlineStr"/>
+      <c r="GG11" t="inlineStr"/>
+      <c r="GH11" t="inlineStr"/>
+      <c r="GI11" t="inlineStr"/>
+      <c r="GJ11" t="inlineStr"/>
+      <c r="GK11" t="inlineStr"/>
+      <c r="GL11" t="inlineStr"/>
+      <c r="GM11" t="inlineStr"/>
+      <c r="GN11" t="inlineStr"/>
+      <c r="GO11" t="inlineStr"/>
+      <c r="GP11" t="inlineStr"/>
+      <c r="GQ11" t="inlineStr"/>
+      <c r="GR11" t="inlineStr"/>
+      <c r="GS11" t="inlineStr"/>
+      <c r="GT11" t="inlineStr"/>
+      <c r="GU11" t="inlineStr"/>
+      <c r="GV11" t="inlineStr"/>
+      <c r="GW11" t="inlineStr"/>
+      <c r="GX11" t="inlineStr"/>
+      <c r="GY11" t="inlineStr"/>
+      <c r="GZ11" t="inlineStr"/>
+      <c r="HA11" t="inlineStr"/>
+      <c r="HB11" t="inlineStr"/>
+      <c r="HC11" t="inlineStr"/>
+      <c r="HD11" t="inlineStr"/>
+      <c r="HE11" t="inlineStr"/>
+      <c r="HF11" t="inlineStr"/>
+      <c r="HG11" t="inlineStr"/>
+      <c r="HH11" t="inlineStr"/>
+      <c r="HI11" t="inlineStr"/>
+      <c r="HJ11" t="inlineStr"/>
+      <c r="HK11" t="inlineStr"/>
+      <c r="HL11" t="inlineStr"/>
+      <c r="HM11" t="inlineStr"/>
+      <c r="HN11" t="inlineStr"/>
+      <c r="HO11" t="inlineStr"/>
+      <c r="HP11" t="inlineStr"/>
+      <c r="HQ11" t="inlineStr"/>
+      <c r="HR11" t="inlineStr"/>
+      <c r="HS11" t="inlineStr"/>
+      <c r="HT11" t="inlineStr"/>
+      <c r="HU11" t="inlineStr"/>
+      <c r="HV11" t="inlineStr"/>
+      <c r="HW11" t="inlineStr"/>
+      <c r="HX11" t="inlineStr"/>
+      <c r="HY11" t="inlineStr"/>
+      <c r="HZ11" t="inlineStr"/>
+      <c r="IA11" t="inlineStr"/>
+      <c r="IB11" t="inlineStr"/>
+      <c r="IC11" t="inlineStr"/>
+      <c r="ID11" t="inlineStr"/>
+      <c r="IE11" t="inlineStr"/>
+      <c r="IF11" t="inlineStr"/>
+      <c r="IG11" t="inlineStr"/>
+      <c r="IH11" t="inlineStr"/>
+      <c r="II11" t="inlineStr"/>
+      <c r="IJ11" t="inlineStr"/>
+      <c r="IK11" t="inlineStr"/>
+      <c r="IL11" t="inlineStr"/>
+      <c r="IM11" t="inlineStr"/>
+      <c r="IN11" t="inlineStr"/>
+      <c r="IO11" t="inlineStr"/>
+      <c r="IP11" t="inlineStr"/>
+      <c r="IQ11" t="inlineStr"/>
+      <c r="IR11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.bosch-home.com/us/en/product/SHEM63W55N</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1515810</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SHEM63W55N</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>SHEM63W55N Bosch 300 Series Dishwasher 46 dBA 120V 12A White</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>BSH Home Appliances</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SHEM63W55N</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Bosch, Dishwasher, 300 Series, SHEM63W55N, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN PLS 120V 12A 46DBA</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Bosch® 300 Series SHEM63W55N Dishwasher, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Bosch® Dishwasher, 300 Series, 120 V, 12 A, Built-in Mounting, 46 dBA Sound Level</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>300 Series Dishwasher, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>300 Series</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr"/>
+      <c r="CJ12" t="inlineStr"/>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="inlineStr"/>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="inlineStr"/>
+      <c r="DK12" t="inlineStr"/>
+      <c r="DL12" t="inlineStr"/>
+      <c r="DM12" t="inlineStr"/>
+      <c r="DN12" t="inlineStr"/>
+      <c r="DO12" t="inlineStr"/>
+      <c r="DP12" t="inlineStr"/>
+      <c r="DQ12" t="inlineStr"/>
+      <c r="DR12" t="inlineStr"/>
+      <c r="DS12" t="inlineStr"/>
+      <c r="DT12" t="inlineStr"/>
+      <c r="DU12" t="inlineStr"/>
+      <c r="DV12" t="inlineStr"/>
+      <c r="DW12" t="inlineStr"/>
+      <c r="DX12" t="inlineStr"/>
+      <c r="DY12" t="inlineStr"/>
+      <c r="DZ12" t="inlineStr"/>
+      <c r="EA12" t="inlineStr"/>
+      <c r="EB12" t="inlineStr"/>
+      <c r="EC12" t="inlineStr"/>
+      <c r="ED12" t="inlineStr"/>
+      <c r="EE12" t="inlineStr"/>
+      <c r="EF12" t="inlineStr"/>
+      <c r="EG12" t="inlineStr"/>
+      <c r="EH12" t="inlineStr"/>
+      <c r="EI12" t="inlineStr"/>
+      <c r="EJ12" t="inlineStr"/>
+      <c r="EK12" t="inlineStr"/>
+      <c r="EL12" t="inlineStr"/>
+      <c r="EM12" t="inlineStr"/>
+      <c r="EN12" t="inlineStr"/>
+      <c r="EO12" t="inlineStr"/>
+      <c r="EP12" t="inlineStr"/>
+      <c r="EQ12" t="inlineStr"/>
+      <c r="ER12" t="inlineStr"/>
+      <c r="ES12" t="inlineStr"/>
+      <c r="ET12" t="inlineStr"/>
+      <c r="EU12" t="inlineStr"/>
+      <c r="EV12" t="inlineStr"/>
+      <c r="EW12" t="inlineStr"/>
+      <c r="EX12" t="inlineStr"/>
+      <c r="EY12" t="inlineStr"/>
+      <c r="EZ12" t="inlineStr"/>
+      <c r="FA12" t="inlineStr"/>
+      <c r="FB12" t="inlineStr"/>
+      <c r="FC12" t="inlineStr"/>
+      <c r="FD12" t="inlineStr"/>
+      <c r="FE12" t="inlineStr"/>
+      <c r="FF12" t="inlineStr"/>
+      <c r="FG12" t="inlineStr"/>
+      <c r="FH12" t="inlineStr"/>
+      <c r="FI12" t="inlineStr"/>
+      <c r="FJ12" t="inlineStr"/>
+      <c r="FK12" t="inlineStr"/>
+      <c r="FL12" t="inlineStr"/>
+      <c r="FM12" t="inlineStr"/>
+      <c r="FN12" t="inlineStr"/>
+      <c r="FO12" t="inlineStr"/>
+      <c r="FP12" t="inlineStr"/>
+      <c r="FQ12" t="inlineStr"/>
+      <c r="FR12" t="inlineStr"/>
+      <c r="FS12" t="inlineStr"/>
+      <c r="FT12" t="inlineStr"/>
+      <c r="FU12" t="inlineStr"/>
+      <c r="FV12" t="inlineStr"/>
+      <c r="FW12" t="inlineStr"/>
+      <c r="FX12" t="inlineStr"/>
+      <c r="FY12" t="inlineStr"/>
+      <c r="FZ12" t="inlineStr"/>
+      <c r="GA12" t="inlineStr"/>
+      <c r="GB12" t="inlineStr"/>
+      <c r="GC12" t="inlineStr"/>
+      <c r="GD12" t="inlineStr"/>
+      <c r="GE12" t="inlineStr"/>
+      <c r="GF12" t="inlineStr"/>
+      <c r="GG12" t="inlineStr"/>
+      <c r="GH12" t="inlineStr"/>
+      <c r="GI12" t="inlineStr"/>
+      <c r="GJ12" t="inlineStr"/>
+      <c r="GK12" t="inlineStr"/>
+      <c r="GL12" t="inlineStr"/>
+      <c r="GM12" t="inlineStr"/>
+      <c r="GN12" t="inlineStr"/>
+      <c r="GO12" t="inlineStr"/>
+      <c r="GP12" t="inlineStr"/>
+      <c r="GQ12" t="inlineStr"/>
+      <c r="GR12" t="inlineStr"/>
+      <c r="GS12" t="inlineStr"/>
+      <c r="GT12" t="inlineStr"/>
+      <c r="GU12" t="inlineStr"/>
+      <c r="GV12" t="inlineStr"/>
+      <c r="GW12" t="inlineStr"/>
+      <c r="GX12" t="inlineStr"/>
+      <c r="GY12" t="inlineStr"/>
+      <c r="GZ12" t="inlineStr"/>
+      <c r="HA12" t="inlineStr"/>
+      <c r="HB12" t="inlineStr"/>
+      <c r="HC12" t="inlineStr"/>
+      <c r="HD12" t="inlineStr"/>
+      <c r="HE12" t="inlineStr"/>
+      <c r="HF12" t="inlineStr"/>
+      <c r="HG12" t="inlineStr"/>
+      <c r="HH12" t="inlineStr"/>
+      <c r="HI12" t="inlineStr"/>
+      <c r="HJ12" t="inlineStr"/>
+      <c r="HK12" t="inlineStr"/>
+      <c r="HL12" t="inlineStr"/>
+      <c r="HM12" t="inlineStr"/>
+      <c r="HN12" t="inlineStr"/>
+      <c r="HO12" t="inlineStr"/>
+      <c r="HP12" t="inlineStr"/>
+      <c r="HQ12" t="inlineStr"/>
+      <c r="HR12" t="inlineStr"/>
+      <c r="HS12" t="inlineStr"/>
+      <c r="HT12" t="inlineStr"/>
+      <c r="HU12" t="inlineStr"/>
+      <c r="HV12" t="inlineStr"/>
+      <c r="HW12" t="inlineStr"/>
+      <c r="HX12" t="inlineStr"/>
+      <c r="HY12" t="inlineStr"/>
+      <c r="HZ12" t="inlineStr"/>
+      <c r="IA12" t="inlineStr"/>
+      <c r="IB12" t="inlineStr"/>
+      <c r="IC12" t="inlineStr"/>
+      <c r="ID12" t="inlineStr"/>
+      <c r="IE12" t="inlineStr"/>
+      <c r="IF12" t="inlineStr"/>
+      <c r="IG12" t="inlineStr"/>
+      <c r="IH12" t="inlineStr"/>
+      <c r="II12" t="inlineStr"/>
+      <c r="IJ12" t="inlineStr"/>
+      <c r="IK12" t="inlineStr"/>
+      <c r="IL12" t="inlineStr"/>
+      <c r="IM12" t="inlineStr"/>
+      <c r="IN12" t="inlineStr"/>
+      <c r="IO12" t="inlineStr"/>
+      <c r="IP12" t="inlineStr"/>
+      <c r="IQ12" t="inlineStr"/>
+      <c r="IR12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1515811</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>KDPE234GPS</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>KDPE234GPS KitchenAid 39 dBA Dishwasher FreeFlex Stainless Steel</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Fastenal Company</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Whirlpool Corporation</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>KitchenAid</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>KDPE234GPS</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>KitchenAid, Dishwasher, PrintShield Series, KDPE234GPS, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 39DBA</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>KitchenAid® PrintShield Series KDPE234GPS Dishwasher, Built-in Mounting, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>KitchenAid® Dishwasher, PrintShield Series, 120 V, 15 A, Built-in Mounting, 39 dBA Sound Level, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>PrintShield Series Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>PrintShield Series</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO13" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="inlineStr"/>
+      <c r="DK13" t="inlineStr"/>
+      <c r="DL13" t="inlineStr"/>
+      <c r="DM13" t="inlineStr"/>
+      <c r="DN13" t="inlineStr"/>
+      <c r="DO13" t="inlineStr"/>
+      <c r="DP13" t="inlineStr"/>
+      <c r="DQ13" t="inlineStr"/>
+      <c r="DR13" t="inlineStr"/>
+      <c r="DS13" t="inlineStr"/>
+      <c r="DT13" t="inlineStr"/>
+      <c r="DU13" t="inlineStr"/>
+      <c r="DV13" t="inlineStr"/>
+      <c r="DW13" t="inlineStr"/>
+      <c r="DX13" t="inlineStr"/>
+      <c r="DY13" t="inlineStr"/>
+      <c r="DZ13" t="inlineStr"/>
+      <c r="EA13" t="inlineStr"/>
+      <c r="EB13" t="inlineStr"/>
+      <c r="EC13" t="inlineStr"/>
+      <c r="ED13" t="inlineStr"/>
+      <c r="EE13" t="inlineStr"/>
+      <c r="EF13" t="inlineStr"/>
+      <c r="EG13" t="inlineStr"/>
+      <c r="EH13" t="inlineStr"/>
+      <c r="EI13" t="inlineStr"/>
+      <c r="EJ13" t="inlineStr"/>
+      <c r="EK13" t="inlineStr"/>
+      <c r="EL13" t="inlineStr"/>
+      <c r="EM13" t="inlineStr"/>
+      <c r="EN13" t="inlineStr"/>
+      <c r="EO13" t="inlineStr"/>
+      <c r="EP13" t="inlineStr"/>
+      <c r="EQ13" t="inlineStr"/>
+      <c r="ER13" t="inlineStr"/>
+      <c r="ES13" t="inlineStr"/>
+      <c r="ET13" t="inlineStr"/>
+      <c r="EU13" t="inlineStr"/>
+      <c r="EV13" t="inlineStr"/>
+      <c r="EW13" t="inlineStr"/>
+      <c r="EX13" t="inlineStr"/>
+      <c r="EY13" t="inlineStr"/>
+      <c r="EZ13" t="inlineStr"/>
+      <c r="FA13" t="inlineStr"/>
+      <c r="FB13" t="inlineStr"/>
+      <c r="FC13" t="inlineStr"/>
+      <c r="FD13" t="inlineStr"/>
+      <c r="FE13" t="inlineStr"/>
+      <c r="FF13" t="inlineStr"/>
+      <c r="FG13" t="inlineStr"/>
+      <c r="FH13" t="inlineStr"/>
+      <c r="FI13" t="inlineStr"/>
+      <c r="FJ13" t="inlineStr"/>
+      <c r="FK13" t="inlineStr"/>
+      <c r="FL13" t="inlineStr"/>
+      <c r="FM13" t="inlineStr"/>
+      <c r="FN13" t="inlineStr"/>
+      <c r="FO13" t="inlineStr"/>
+      <c r="FP13" t="inlineStr"/>
+      <c r="FQ13" t="inlineStr"/>
+      <c r="FR13" t="inlineStr"/>
+      <c r="FS13" t="inlineStr"/>
+      <c r="FT13" t="inlineStr"/>
+      <c r="FU13" t="inlineStr"/>
+      <c r="FV13" t="inlineStr"/>
+      <c r="FW13" t="inlineStr"/>
+      <c r="FX13" t="inlineStr"/>
+      <c r="FY13" t="inlineStr"/>
+      <c r="FZ13" t="inlineStr"/>
+      <c r="GA13" t="inlineStr"/>
+      <c r="GB13" t="inlineStr"/>
+      <c r="GC13" t="inlineStr"/>
+      <c r="GD13" t="inlineStr"/>
+      <c r="GE13" t="inlineStr"/>
+      <c r="GF13" t="inlineStr"/>
+      <c r="GG13" t="inlineStr"/>
+      <c r="GH13" t="inlineStr"/>
+      <c r="GI13" t="inlineStr"/>
+      <c r="GJ13" t="inlineStr"/>
+      <c r="GK13" t="inlineStr"/>
+      <c r="GL13" t="inlineStr"/>
+      <c r="GM13" t="inlineStr"/>
+      <c r="GN13" t="inlineStr"/>
+      <c r="GO13" t="inlineStr"/>
+      <c r="GP13" t="inlineStr"/>
+      <c r="GQ13" t="inlineStr"/>
+      <c r="GR13" t="inlineStr"/>
+      <c r="GS13" t="inlineStr"/>
+      <c r="GT13" t="inlineStr"/>
+      <c r="GU13" t="inlineStr"/>
+      <c r="GV13" t="inlineStr"/>
+      <c r="GW13" t="inlineStr"/>
+      <c r="GX13" t="inlineStr"/>
+      <c r="GY13" t="inlineStr"/>
+      <c r="GZ13" t="inlineStr"/>
+      <c r="HA13" t="inlineStr"/>
+      <c r="HB13" t="inlineStr"/>
+      <c r="HC13" t="inlineStr"/>
+      <c r="HD13" t="inlineStr"/>
+      <c r="HE13" t="inlineStr"/>
+      <c r="HF13" t="inlineStr"/>
+      <c r="HG13" t="inlineStr"/>
+      <c r="HH13" t="inlineStr"/>
+      <c r="HI13" t="inlineStr"/>
+      <c r="HJ13" t="inlineStr"/>
+      <c r="HK13" t="inlineStr"/>
+      <c r="HL13" t="inlineStr"/>
+      <c r="HM13" t="inlineStr"/>
+      <c r="HN13" t="inlineStr"/>
+      <c r="HO13" t="inlineStr"/>
+      <c r="HP13" t="inlineStr"/>
+      <c r="HQ13" t="inlineStr"/>
+      <c r="HR13" t="inlineStr"/>
+      <c r="HS13" t="inlineStr"/>
+      <c r="HT13" t="inlineStr"/>
+      <c r="HU13" t="inlineStr"/>
+      <c r="HV13" t="inlineStr"/>
+      <c r="HW13" t="inlineStr"/>
+      <c r="HX13" t="inlineStr"/>
+      <c r="HY13" t="inlineStr"/>
+      <c r="HZ13" t="inlineStr"/>
+      <c r="IA13" t="inlineStr"/>
+      <c r="IB13" t="inlineStr"/>
+      <c r="IC13" t="inlineStr"/>
+      <c r="ID13" t="inlineStr"/>
+      <c r="IE13" t="inlineStr"/>
+      <c r="IF13" t="inlineStr"/>
+      <c r="IG13" t="inlineStr"/>
+      <c r="IH13" t="inlineStr"/>
+      <c r="II13" t="inlineStr"/>
+      <c r="IJ13" t="inlineStr"/>
+      <c r="IK13" t="inlineStr"/>
+      <c r="IL13" t="inlineStr"/>
+      <c r="IM13" t="inlineStr"/>
+      <c r="IN13" t="inlineStr"/>
+      <c r="IO13" t="inlineStr"/>
+      <c r="IP13" t="inlineStr"/>
+      <c r="IQ13" t="inlineStr"/>
+      <c r="IR13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1515812</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>G7106SCVi</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>G7106SCVi Miele Fully Integrated Dishwasher 42 dBA 120V 15A Panel Ready</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Grainger Industrial Supply</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Miele Inc.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Miele</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>G7106SCVi</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Miele, Dishwasher, G7106SCVi, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN PLS 120V 15A 42DBA</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Miele® G7106SCVi Dishwasher, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Miele® Dishwasher, 120 V, 15 A, Built-in Mounting, 42 dBA Sound Level</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Dishwasher, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="CM14" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN14" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="inlineStr"/>
+      <c r="DG14" t="inlineStr"/>
+      <c r="DH14" t="inlineStr"/>
+      <c r="DI14" t="inlineStr"/>
+      <c r="DJ14" t="inlineStr"/>
+      <c r="DK14" t="inlineStr"/>
+      <c r="DL14" t="inlineStr"/>
+      <c r="DM14" t="inlineStr"/>
+      <c r="DN14" t="inlineStr"/>
+      <c r="DO14" t="inlineStr"/>
+      <c r="DP14" t="inlineStr"/>
+      <c r="DQ14" t="inlineStr"/>
+      <c r="DR14" t="inlineStr"/>
+      <c r="DS14" t="inlineStr"/>
+      <c r="DT14" t="inlineStr"/>
+      <c r="DU14" t="inlineStr"/>
+      <c r="DV14" t="inlineStr"/>
+      <c r="DW14" t="inlineStr"/>
+      <c r="DX14" t="inlineStr"/>
+      <c r="DY14" t="inlineStr"/>
+      <c r="DZ14" t="inlineStr"/>
+      <c r="EA14" t="inlineStr"/>
+      <c r="EB14" t="inlineStr"/>
+      <c r="EC14" t="inlineStr"/>
+      <c r="ED14" t="inlineStr"/>
+      <c r="EE14" t="inlineStr"/>
+      <c r="EF14" t="inlineStr"/>
+      <c r="EG14" t="inlineStr"/>
+      <c r="EH14" t="inlineStr"/>
+      <c r="EI14" t="inlineStr"/>
+      <c r="EJ14" t="inlineStr"/>
+      <c r="EK14" t="inlineStr"/>
+      <c r="EL14" t="inlineStr"/>
+      <c r="EM14" t="inlineStr"/>
+      <c r="EN14" t="inlineStr"/>
+      <c r="EO14" t="inlineStr"/>
+      <c r="EP14" t="inlineStr"/>
+      <c r="EQ14" t="inlineStr"/>
+      <c r="ER14" t="inlineStr"/>
+      <c r="ES14" t="inlineStr"/>
+      <c r="ET14" t="inlineStr"/>
+      <c r="EU14" t="inlineStr"/>
+      <c r="EV14" t="inlineStr"/>
+      <c r="EW14" t="inlineStr"/>
+      <c r="EX14" t="inlineStr"/>
+      <c r="EY14" t="inlineStr"/>
+      <c r="EZ14" t="inlineStr"/>
+      <c r="FA14" t="inlineStr"/>
+      <c r="FB14" t="inlineStr"/>
+      <c r="FC14" t="inlineStr"/>
+      <c r="FD14" t="inlineStr"/>
+      <c r="FE14" t="inlineStr"/>
+      <c r="FF14" t="inlineStr"/>
+      <c r="FG14" t="inlineStr"/>
+      <c r="FH14" t="inlineStr"/>
+      <c r="FI14" t="inlineStr"/>
+      <c r="FJ14" t="inlineStr"/>
+      <c r="FK14" t="inlineStr"/>
+      <c r="FL14" t="inlineStr"/>
+      <c r="FM14" t="inlineStr"/>
+      <c r="FN14" t="inlineStr"/>
+      <c r="FO14" t="inlineStr"/>
+      <c r="FP14" t="inlineStr"/>
+      <c r="FQ14" t="inlineStr"/>
+      <c r="FR14" t="inlineStr"/>
+      <c r="FS14" t="inlineStr"/>
+      <c r="FT14" t="inlineStr"/>
+      <c r="FU14" t="inlineStr"/>
+      <c r="FV14" t="inlineStr"/>
+      <c r="FW14" t="inlineStr"/>
+      <c r="FX14" t="inlineStr"/>
+      <c r="FY14" t="inlineStr"/>
+      <c r="FZ14" t="inlineStr"/>
+      <c r="GA14" t="inlineStr"/>
+      <c r="GB14" t="inlineStr"/>
+      <c r="GC14" t="inlineStr"/>
+      <c r="GD14" t="inlineStr"/>
+      <c r="GE14" t="inlineStr"/>
+      <c r="GF14" t="inlineStr"/>
+      <c r="GG14" t="inlineStr"/>
+      <c r="GH14" t="inlineStr"/>
+      <c r="GI14" t="inlineStr"/>
+      <c r="GJ14" t="inlineStr"/>
+      <c r="GK14" t="inlineStr"/>
+      <c r="GL14" t="inlineStr"/>
+      <c r="GM14" t="inlineStr"/>
+      <c r="GN14" t="inlineStr"/>
+      <c r="GO14" t="inlineStr"/>
+      <c r="GP14" t="inlineStr"/>
+      <c r="GQ14" t="inlineStr"/>
+      <c r="GR14" t="inlineStr"/>
+      <c r="GS14" t="inlineStr"/>
+      <c r="GT14" t="inlineStr"/>
+      <c r="GU14" t="inlineStr"/>
+      <c r="GV14" t="inlineStr"/>
+      <c r="GW14" t="inlineStr"/>
+      <c r="GX14" t="inlineStr"/>
+      <c r="GY14" t="inlineStr"/>
+      <c r="GZ14" t="inlineStr"/>
+      <c r="HA14" t="inlineStr"/>
+      <c r="HB14" t="inlineStr"/>
+      <c r="HC14" t="inlineStr"/>
+      <c r="HD14" t="inlineStr"/>
+      <c r="HE14" t="inlineStr"/>
+      <c r="HF14" t="inlineStr"/>
+      <c r="HG14" t="inlineStr"/>
+      <c r="HH14" t="inlineStr"/>
+      <c r="HI14" t="inlineStr"/>
+      <c r="HJ14" t="inlineStr"/>
+      <c r="HK14" t="inlineStr"/>
+      <c r="HL14" t="inlineStr"/>
+      <c r="HM14" t="inlineStr"/>
+      <c r="HN14" t="inlineStr"/>
+      <c r="HO14" t="inlineStr"/>
+      <c r="HP14" t="inlineStr"/>
+      <c r="HQ14" t="inlineStr"/>
+      <c r="HR14" t="inlineStr"/>
+      <c r="HS14" t="inlineStr"/>
+      <c r="HT14" t="inlineStr"/>
+      <c r="HU14" t="inlineStr"/>
+      <c r="HV14" t="inlineStr"/>
+      <c r="HW14" t="inlineStr"/>
+      <c r="HX14" t="inlineStr"/>
+      <c r="HY14" t="inlineStr"/>
+      <c r="HZ14" t="inlineStr"/>
+      <c r="IA14" t="inlineStr"/>
+      <c r="IB14" t="inlineStr"/>
+      <c r="IC14" t="inlineStr"/>
+      <c r="ID14" t="inlineStr"/>
+      <c r="IE14" t="inlineStr"/>
+      <c r="IF14" t="inlineStr"/>
+      <c r="IG14" t="inlineStr"/>
+      <c r="IH14" t="inlineStr"/>
+      <c r="II14" t="inlineStr"/>
+      <c r="IJ14" t="inlineStr"/>
+      <c r="IK14" t="inlineStr"/>
+      <c r="IL14" t="inlineStr"/>
+      <c r="IM14" t="inlineStr"/>
+      <c r="IN14" t="inlineStr"/>
+      <c r="IO14" t="inlineStr"/>
+      <c r="IP14" t="inlineStr"/>
+      <c r="IQ14" t="inlineStr"/>
+      <c r="IR14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1515813</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>WDF520PADM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>WDF520PADM Whirlpool Front Control Dishwasher 55 dBA 120V 12A White</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Whirlpool Corporation</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Whirlpool®</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>WDF520PADM</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Whirlpool, Dishwasher, Eco Series, WDF520PADM, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN PLS 120V 12A 55DBA</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Whirlpool® Eco Series WDF520PADM Dishwasher, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Whirlpool® Dishwasher, Eco Series, 120 V, 12 A, Built-in Mounting, 55 dBA Sound Level</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Eco Series Dishwasher, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>Eco Series</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr"/>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN15" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="inlineStr"/>
+      <c r="DJ15" t="inlineStr"/>
+      <c r="DK15" t="inlineStr"/>
+      <c r="DL15" t="inlineStr"/>
+      <c r="DM15" t="inlineStr"/>
+      <c r="DN15" t="inlineStr"/>
+      <c r="DO15" t="inlineStr"/>
+      <c r="DP15" t="inlineStr"/>
+      <c r="DQ15" t="inlineStr"/>
+      <c r="DR15" t="inlineStr"/>
+      <c r="DS15" t="inlineStr"/>
+      <c r="DT15" t="inlineStr"/>
+      <c r="DU15" t="inlineStr"/>
+      <c r="DV15" t="inlineStr"/>
+      <c r="DW15" t="inlineStr"/>
+      <c r="DX15" t="inlineStr"/>
+      <c r="DY15" t="inlineStr"/>
+      <c r="DZ15" t="inlineStr"/>
+      <c r="EA15" t="inlineStr"/>
+      <c r="EB15" t="inlineStr"/>
+      <c r="EC15" t="inlineStr"/>
+      <c r="ED15" t="inlineStr"/>
+      <c r="EE15" t="inlineStr"/>
+      <c r="EF15" t="inlineStr"/>
+      <c r="EG15" t="inlineStr"/>
+      <c r="EH15" t="inlineStr"/>
+      <c r="EI15" t="inlineStr"/>
+      <c r="EJ15" t="inlineStr"/>
+      <c r="EK15" t="inlineStr"/>
+      <c r="EL15" t="inlineStr"/>
+      <c r="EM15" t="inlineStr"/>
+      <c r="EN15" t="inlineStr"/>
+      <c r="EO15" t="inlineStr"/>
+      <c r="EP15" t="inlineStr"/>
+      <c r="EQ15" t="inlineStr"/>
+      <c r="ER15" t="inlineStr"/>
+      <c r="ES15" t="inlineStr"/>
+      <c r="ET15" t="inlineStr"/>
+      <c r="EU15" t="inlineStr"/>
+      <c r="EV15" t="inlineStr"/>
+      <c r="EW15" t="inlineStr"/>
+      <c r="EX15" t="inlineStr"/>
+      <c r="EY15" t="inlineStr"/>
+      <c r="EZ15" t="inlineStr"/>
+      <c r="FA15" t="inlineStr"/>
+      <c r="FB15" t="inlineStr"/>
+      <c r="FC15" t="inlineStr"/>
+      <c r="FD15" t="inlineStr"/>
+      <c r="FE15" t="inlineStr"/>
+      <c r="FF15" t="inlineStr"/>
+      <c r="FG15" t="inlineStr"/>
+      <c r="FH15" t="inlineStr"/>
+      <c r="FI15" t="inlineStr"/>
+      <c r="FJ15" t="inlineStr"/>
+      <c r="FK15" t="inlineStr"/>
+      <c r="FL15" t="inlineStr"/>
+      <c r="FM15" t="inlineStr"/>
+      <c r="FN15" t="inlineStr"/>
+      <c r="FO15" t="inlineStr"/>
+      <c r="FP15" t="inlineStr"/>
+      <c r="FQ15" t="inlineStr"/>
+      <c r="FR15" t="inlineStr"/>
+      <c r="FS15" t="inlineStr"/>
+      <c r="FT15" t="inlineStr"/>
+      <c r="FU15" t="inlineStr"/>
+      <c r="FV15" t="inlineStr"/>
+      <c r="FW15" t="inlineStr"/>
+      <c r="FX15" t="inlineStr"/>
+      <c r="FY15" t="inlineStr"/>
+      <c r="FZ15" t="inlineStr"/>
+      <c r="GA15" t="inlineStr"/>
+      <c r="GB15" t="inlineStr"/>
+      <c r="GC15" t="inlineStr"/>
+      <c r="GD15" t="inlineStr"/>
+      <c r="GE15" t="inlineStr"/>
+      <c r="GF15" t="inlineStr"/>
+      <c r="GG15" t="inlineStr"/>
+      <c r="GH15" t="inlineStr"/>
+      <c r="GI15" t="inlineStr"/>
+      <c r="GJ15" t="inlineStr"/>
+      <c r="GK15" t="inlineStr"/>
+      <c r="GL15" t="inlineStr"/>
+      <c r="GM15" t="inlineStr"/>
+      <c r="GN15" t="inlineStr"/>
+      <c r="GO15" t="inlineStr"/>
+      <c r="GP15" t="inlineStr"/>
+      <c r="GQ15" t="inlineStr"/>
+      <c r="GR15" t="inlineStr"/>
+      <c r="GS15" t="inlineStr"/>
+      <c r="GT15" t="inlineStr"/>
+      <c r="GU15" t="inlineStr"/>
+      <c r="GV15" t="inlineStr"/>
+      <c r="GW15" t="inlineStr"/>
+      <c r="GX15" t="inlineStr"/>
+      <c r="GY15" t="inlineStr"/>
+      <c r="GZ15" t="inlineStr"/>
+      <c r="HA15" t="inlineStr"/>
+      <c r="HB15" t="inlineStr"/>
+      <c r="HC15" t="inlineStr"/>
+      <c r="HD15" t="inlineStr"/>
+      <c r="HE15" t="inlineStr"/>
+      <c r="HF15" t="inlineStr"/>
+      <c r="HG15" t="inlineStr"/>
+      <c r="HH15" t="inlineStr"/>
+      <c r="HI15" t="inlineStr"/>
+      <c r="HJ15" t="inlineStr"/>
+      <c r="HK15" t="inlineStr"/>
+      <c r="HL15" t="inlineStr"/>
+      <c r="HM15" t="inlineStr"/>
+      <c r="HN15" t="inlineStr"/>
+      <c r="HO15" t="inlineStr"/>
+      <c r="HP15" t="inlineStr"/>
+      <c r="HQ15" t="inlineStr"/>
+      <c r="HR15" t="inlineStr"/>
+      <c r="HS15" t="inlineStr"/>
+      <c r="HT15" t="inlineStr"/>
+      <c r="HU15" t="inlineStr"/>
+      <c r="HV15" t="inlineStr"/>
+      <c r="HW15" t="inlineStr"/>
+      <c r="HX15" t="inlineStr"/>
+      <c r="HY15" t="inlineStr"/>
+      <c r="HZ15" t="inlineStr"/>
+      <c r="IA15" t="inlineStr"/>
+      <c r="IB15" t="inlineStr"/>
+      <c r="IC15" t="inlineStr"/>
+      <c r="ID15" t="inlineStr"/>
+      <c r="IE15" t="inlineStr"/>
+      <c r="IF15" t="inlineStr"/>
+      <c r="IG15" t="inlineStr"/>
+      <c r="IH15" t="inlineStr"/>
+      <c r="II15" t="inlineStr"/>
+      <c r="IJ15" t="inlineStr"/>
+      <c r="IK15" t="inlineStr"/>
+      <c r="IL15" t="inlineStr"/>
+      <c r="IM15" t="inlineStr"/>
+      <c r="IN15" t="inlineStr"/>
+      <c r="IO15" t="inlineStr"/>
+      <c r="IP15" t="inlineStr"/>
+      <c r="IQ15" t="inlineStr"/>
+      <c r="IR15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1515814</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PDT785SBNTS</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PDT785SBNTS GE Profile Dishwasher 47 dBA 120V 15A Black Stainless Steel</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-- Unbranded --</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>-- No Unilog Brand --</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>-- No DIB Brand --</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>GE Appliances</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>GE Profile</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>PDT785SBNTS</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Consumer Electronics&gt;Kitchen Appliances&gt;Built-In Dishwashers</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>GE Profile, Dishwasher, Profile Series, PDT785SBNTS, Built-in Mounting</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 47DBA</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>GE Profile® Profile Series PDT785SBNTS Dishwasher, Built-in Mounting, Black Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>GE Profile® Dishwasher, Profile Series, 120 V, 15 A, Built-in Mounting, 47 dBA Sound Level, Black Stainless Steel, Black Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Profile Series Dishwasher, Built-in Mounting, Black Stainless Steel, Black Stainless Steel</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>ASSE 1006|CEE Tier 2 Qualified|cUL Listed|ENERGY STAR Certified|NSF Certified|UL Listed</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>Profile Series</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr"/>
+      <c r="CJ16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="CM16" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN16" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO16" t="inlineStr">
+        <is>
+          <t>Black Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>Black Stainless Steel</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="inlineStr"/>
+      <c r="DG16" t="inlineStr"/>
+      <c r="DH16" t="inlineStr"/>
+      <c r="DI16" t="inlineStr"/>
+      <c r="DJ16" t="inlineStr"/>
+      <c r="DK16" t="inlineStr"/>
+      <c r="DL16" t="inlineStr"/>
+      <c r="DM16" t="inlineStr"/>
+      <c r="DN16" t="inlineStr"/>
+      <c r="DO16" t="inlineStr"/>
+      <c r="DP16" t="inlineStr"/>
+      <c r="DQ16" t="inlineStr"/>
+      <c r="DR16" t="inlineStr"/>
+      <c r="DS16" t="inlineStr"/>
+      <c r="DT16" t="inlineStr"/>
+      <c r="DU16" t="inlineStr"/>
+      <c r="DV16" t="inlineStr"/>
+      <c r="DW16" t="inlineStr"/>
+      <c r="DX16" t="inlineStr"/>
+      <c r="DY16" t="inlineStr"/>
+      <c r="DZ16" t="inlineStr"/>
+      <c r="EA16" t="inlineStr"/>
+      <c r="EB16" t="inlineStr"/>
+      <c r="EC16" t="inlineStr"/>
+      <c r="ED16" t="inlineStr"/>
+      <c r="EE16" t="inlineStr"/>
+      <c r="EF16" t="inlineStr"/>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr"/>
+      <c r="EI16" t="inlineStr"/>
+      <c r="EJ16" t="inlineStr"/>
+      <c r="EK16" t="inlineStr"/>
+      <c r="EL16" t="inlineStr"/>
+      <c r="EM16" t="inlineStr"/>
+      <c r="EN16" t="inlineStr"/>
+      <c r="EO16" t="inlineStr"/>
+      <c r="EP16" t="inlineStr"/>
+      <c r="EQ16" t="inlineStr"/>
+      <c r="ER16" t="inlineStr"/>
+      <c r="ES16" t="inlineStr"/>
+      <c r="ET16" t="inlineStr"/>
+      <c r="EU16" t="inlineStr"/>
+      <c r="EV16" t="inlineStr"/>
+      <c r="EW16" t="inlineStr"/>
+      <c r="EX16" t="inlineStr"/>
+      <c r="EY16" t="inlineStr"/>
+      <c r="EZ16" t="inlineStr"/>
+      <c r="FA16" t="inlineStr"/>
+      <c r="FB16" t="inlineStr"/>
+      <c r="FC16" t="inlineStr"/>
+      <c r="FD16" t="inlineStr"/>
+      <c r="FE16" t="inlineStr"/>
+      <c r="FF16" t="inlineStr"/>
+      <c r="FG16" t="inlineStr"/>
+      <c r="FH16" t="inlineStr"/>
+      <c r="FI16" t="inlineStr"/>
+      <c r="FJ16" t="inlineStr"/>
+      <c r="FK16" t="inlineStr"/>
+      <c r="FL16" t="inlineStr"/>
+      <c r="FM16" t="inlineStr"/>
+      <c r="FN16" t="inlineStr"/>
+      <c r="FO16" t="inlineStr"/>
+      <c r="FP16" t="inlineStr"/>
+      <c r="FQ16" t="inlineStr"/>
+      <c r="FR16" t="inlineStr"/>
+      <c r="FS16" t="inlineStr"/>
+      <c r="FT16" t="inlineStr"/>
+      <c r="FU16" t="inlineStr"/>
+      <c r="FV16" t="inlineStr"/>
+      <c r="FW16" t="inlineStr"/>
+      <c r="FX16" t="inlineStr"/>
+      <c r="FY16" t="inlineStr"/>
+      <c r="FZ16" t="inlineStr"/>
+      <c r="GA16" t="inlineStr"/>
+      <c r="GB16" t="inlineStr"/>
+      <c r="GC16" t="inlineStr"/>
+      <c r="GD16" t="inlineStr"/>
+      <c r="GE16" t="inlineStr"/>
+      <c r="GF16" t="inlineStr"/>
+      <c r="GG16" t="inlineStr"/>
+      <c r="GH16" t="inlineStr"/>
+      <c r="GI16" t="inlineStr"/>
+      <c r="GJ16" t="inlineStr"/>
+      <c r="GK16" t="inlineStr"/>
+      <c r="GL16" t="inlineStr"/>
+      <c r="GM16" t="inlineStr"/>
+      <c r="GN16" t="inlineStr"/>
+      <c r="GO16" t="inlineStr"/>
+      <c r="GP16" t="inlineStr"/>
+      <c r="GQ16" t="inlineStr"/>
+      <c r="GR16" t="inlineStr"/>
+      <c r="GS16" t="inlineStr"/>
+      <c r="GT16" t="inlineStr"/>
+      <c r="GU16" t="inlineStr"/>
+      <c r="GV16" t="inlineStr"/>
+      <c r="GW16" t="inlineStr"/>
+      <c r="GX16" t="inlineStr"/>
+      <c r="GY16" t="inlineStr"/>
+      <c r="GZ16" t="inlineStr"/>
+      <c r="HA16" t="inlineStr"/>
+      <c r="HB16" t="inlineStr"/>
+      <c r="HC16" t="inlineStr"/>
+      <c r="HD16" t="inlineStr"/>
+      <c r="HE16" t="inlineStr"/>
+      <c r="HF16" t="inlineStr"/>
+      <c r="HG16" t="inlineStr"/>
+      <c r="HH16" t="inlineStr"/>
+      <c r="HI16" t="inlineStr"/>
+      <c r="HJ16" t="inlineStr"/>
+      <c r="HK16" t="inlineStr"/>
+      <c r="HL16" t="inlineStr"/>
+      <c r="HM16" t="inlineStr"/>
+      <c r="HN16" t="inlineStr"/>
+      <c r="HO16" t="inlineStr"/>
+      <c r="HP16" t="inlineStr"/>
+      <c r="HQ16" t="inlineStr"/>
+      <c r="HR16" t="inlineStr"/>
+      <c r="HS16" t="inlineStr"/>
+      <c r="HT16" t="inlineStr"/>
+      <c r="HU16" t="inlineStr"/>
+      <c r="HV16" t="inlineStr"/>
+      <c r="HW16" t="inlineStr"/>
+      <c r="HX16" t="inlineStr"/>
+      <c r="HY16" t="inlineStr"/>
+      <c r="HZ16" t="inlineStr"/>
+      <c r="IA16" t="inlineStr"/>
+      <c r="IB16" t="inlineStr"/>
+      <c r="IC16" t="inlineStr"/>
+      <c r="ID16" t="inlineStr"/>
+      <c r="IE16" t="inlineStr"/>
+      <c r="IF16" t="inlineStr"/>
+      <c r="IG16" t="inlineStr"/>
+      <c r="IH16" t="inlineStr"/>
+      <c r="II16" t="inlineStr"/>
+      <c r="IJ16" t="inlineStr"/>
+      <c r="IK16" t="inlineStr"/>
+      <c r="IL16" t="inlineStr"/>
+      <c r="IM16" t="inlineStr"/>
+      <c r="IN16" t="inlineStr"/>
+      <c r="IO16" t="inlineStr"/>
+      <c r="IP16" t="inlineStr"/>
+      <c r="IQ16" t="inlineStr"/>
+      <c r="IR16" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/data/output/delivery_export.xlsx
+++ b/data/output/delivery_export.xlsx
@@ -9552,12 +9552,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>UNRESOLVED — needs manual review</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>UNRESOLVED — needs manual review</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>LG, Uncategorized, SF-3001</t>
+          <t>UNRESOLVED — needs manual review, Uncategorized, SF-3001</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>LG SF-3001 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review SF-3001 Uncategorized</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>LG Uncategorized, SF-3001</t>
+          <t>UNRESOLVED — needs manual review Uncategorized, SF-3001</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>UNRESOLVED — needs manual review</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>UNRESOLVED — needs manual review</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>LG, Power Tools, LG-7001</t>
+          <t>UNRESOLVED — needs manual review, Power Tools, LG-7001</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>LG LG-7001 Power Tools, 40</t>
+          <t>UNRESOLVED — needs manual review LG-7001 Power Tools, 40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>LG Power Tools, LG-7001, 40</t>
+          <t>UNRESOLVED — needs manual review Power Tools, LG-7001, 40</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -12578,12 +12578,12 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>UNRESOLVED — needs manual review</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>UNRESOLVED — needs manual review</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>LG, Power Tools, LG-7002</t>
+          <t>UNRESOLVED — needs manual review, Power Tools, LG-7002</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -12610,12 +12610,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>LG LG-7002 Power Tools, 40</t>
+          <t>UNRESOLVED — needs manual review LG-7002 Power Tools, 40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>LG Power Tools, LG-7002, 40</t>
+          <t>UNRESOLVED — needs manual review Power Tools, LG-7002, 40</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">

--- a/data/output/delivery_export.xlsx
+++ b/data/output/delivery_export.xlsx
@@ -1690,22 +1690,30 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K2" t="n">
         <v>1515800</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>AB-3301</t>
+          <t>MDB8959SKZ</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3M CUBITRON II 60GRIT 4.5IN CUT-OFF WHL</t>
+          <t>MDB8959SKZ Maytag Top Control Dishwasher 47 dBA 120V 15A Stainless Steel</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1725,54 +1733,54 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3M Company</t>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Whirlpool Corporation</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Maytag</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>AB-3301</t>
+          <t>MDB8959SKZ</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, AB-3301</t>
+          <t>Maytag, Dishwasher, MDB8959SKZ, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED AB-3301 60 GRIT</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 47DBA</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review AB-3301 Uncategorized, 60</t>
+          <t>Maytag® MDB8959SKZ Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, AB-3301, 60</t>
+          <t>Maytag® Dishwasher, 120 V, 15 A, Built-in Mounting, 47 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Uncategorized, 60</t>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -1803,60 +1811,148 @@
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>Grit</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW2" t="inlineStr"/>
       <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ2" t="inlineStr"/>
       <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC2" t="inlineStr"/>
       <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr"/>
-      <c r="CH2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="inlineStr"/>
-      <c r="CK2" t="inlineStr"/>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="inlineStr"/>
-      <c r="CO2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
-      <c r="CR2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="inlineStr"/>
@@ -2028,22 +2124,30 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K3" t="n">
         <v>1515801</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AB-3302</t>
+          <t>DWHD650WFP</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>60 GRT CUTOFF DISC 4-1/2IN</t>
+          <t>DWHD650WFP Thermador Sapphire Series Dishwasher 40 dBA 120V 15A Panel Ready</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2063,54 +2167,54 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3M Co.</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>BSH Home Appliances</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Thermador</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>AB-3302</t>
+          <t>DWHD650WFP</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, AB-3302</t>
+          <t>Thermador, Dishwasher, DWHD650WFP, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED AB-3302</t>
+          <t>DISHWASHER BLTLN PLS 120V 15A 40DBA</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review AB-3302 Uncategorized</t>
+          <t>Thermador® DWHD650WFP Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, AB-3302</t>
+          <t>Thermador® Dishwasher, 120 V, 15 A, Built-in Mounting, 40 dBA Sound Level</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -2141,52 +2245,140 @@
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW3" t="inlineStr"/>
       <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="inlineStr"/>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
       <c r="CO3" t="inlineStr"/>
       <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
       <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="inlineStr"/>
@@ -2358,22 +2550,30 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Abrasives</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K4" t="n">
         <v>1515802</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AB-4401</t>
+          <t>BDF450</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>7IN GRINDING WHL A24 TYPE 27</t>
+          <t>BDF450 Beko Front Control Dishwasher 45 dBA 120V 12A Stainless Steel</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2393,54 +2593,54 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Norton Abrasives</t>
+          <t>MSC Industrial Supply</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Arçelik</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Beko</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>AB-4401</t>
+          <t>BDF450</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Abrasives</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Abrasives, AB-4401</t>
+          <t>Beko, Dishwasher, BDF450, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ABRASIVES AB-4401</t>
+          <t>DISHWASHER BLTLN SST SST 120V 12A 45DBA</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review AB-4401 Abrasives</t>
+          <t>Beko® BDF450 Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Abrasives, AB-4401</t>
+          <t>Beko® Dishwasher, 120 V, 12 A, Built-in Mounting, 45 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Abrasives</t>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -2471,52 +2671,148 @@
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr"/>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW4" t="inlineStr"/>
       <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ4" t="inlineStr"/>
       <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC4" t="inlineStr"/>
       <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr"/>
-      <c r="CH4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI4" t="inlineStr"/>
       <c r="CJ4" t="inlineStr"/>
-      <c r="CK4" t="inlineStr"/>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="inlineStr"/>
-      <c r="CO4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="inlineStr"/>
-      <c r="CR4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="inlineStr"/>
       <c r="CW4" t="inlineStr"/>
@@ -2688,22 +2984,30 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K5" t="n">
         <v>1515803</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>AB-4402</t>
+          <t>DD24SDFT9N</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>GRIND WHEEL 7 IN TYPE27 A24</t>
+          <t>DD24SDFT9N Fisher Paykel Double DishDrawer 44 dBA 120V 15A Stainless Steel</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2723,54 +3027,54 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Norton Abr.</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Fisher &amp; Paykel Appliances</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Fisher &amp; Paykel</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>AB-4402</t>
+          <t>DD24SDFT9N</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, AB-4402</t>
+          <t>Fisher &amp; Paykel, Dishwasher, DD24SDFT9N, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED AB-4402</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 44DBA</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review AB-4402 Uncategorized</t>
+          <t>Fisher &amp; Paykel® DD24SDFT9N Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, AB-4402</t>
+          <t>Fisher &amp; Paykel® Dishwasher, 120 V, 15 A, Built-in Mounting, 44 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -2801,52 +3105,148 @@
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr"/>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW5" t="inlineStr"/>
       <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC5" t="inlineStr"/>
       <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI5" t="inlineStr"/>
       <c r="CJ5" t="inlineStr"/>
-      <c r="CK5" t="inlineStr"/>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="inlineStr"/>
@@ -3018,22 +3418,30 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Abrasives</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K6" t="n">
         <v>1515804</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AB-5501</t>
+          <t>WDT750SAKZ</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>80GRIT SANDING BELT 3X21IN</t>
+          <t>WDT750SAKZ Whirlpool Top Control Dishwasher 47 dBA 120V 15A Fingerprint Resistant</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -3053,54 +3461,54 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3M Company</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Whirlpool Corporation</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Whirlpool®</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>AB-5501</t>
+          <t>WDT750SAKZ</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Abrasives</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Abrasives, AB-5501</t>
+          <t>Whirlpool, Dishwasher, Eco Series, WDT750SAKZ, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>ABRASIVES AB-5501 80 GRIT</t>
+          <t>DISHWASHER BLTLN PLS 120V 15A 47DBA</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review AB-5501 Abrasives, 80</t>
+          <t>Whirlpool® Eco Series WDT750SAKZ Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Abrasives, AB-5501, 80</t>
+          <t>Whirlpool® Dishwasher, Eco Series, 120 V, 15 A, Built-in Mounting, 47 dBA Sound Level</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Abrasives, 80</t>
+          <t>Eco Series Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -3131,60 +3539,144 @@
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>Grit</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>Eco Series</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW6" t="inlineStr"/>
       <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
-      <c r="CE6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr"/>
-      <c r="CH6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI6" t="inlineStr"/>
       <c r="CJ6" t="inlineStr"/>
-      <c r="CK6" t="inlineStr"/>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
-      <c r="CN6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
       <c r="CO6" t="inlineStr"/>
       <c r="CP6" t="inlineStr"/>
-      <c r="CQ6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
       <c r="CR6" t="inlineStr"/>
       <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU6" t="inlineStr"/>
       <c r="CV6" t="inlineStr"/>
       <c r="CW6" t="inlineStr"/>
@@ -3356,22 +3848,30 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lighting</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K7" t="n">
         <v>1515805</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LB-1101</t>
+          <t>KDTM404KPS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>LED A19 9W 2700K DIMMABLE 4PK</t>
+          <t>KDTM404KPS KitchenAid 44 dBA Dishwasher PrintShield Stainless Steel</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -3391,54 +3891,54 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Signify NA</t>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Whirlpool Corporation</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>KitchenAid</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>LB-1101</t>
+          <t>KDTM404KPS</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Lighting, LB-1101</t>
+          <t>KitchenAid, Dishwasher, PrintShield Series, KDTM404KPS, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>LIGHTING LB-1101 9 WATTAGE 2700 COLOR TE</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 44DBA</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review LB-1101 Lighting, 9</t>
+          <t>KitchenAid® PrintShield Series KDTM404KPS Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Lighting, LB-1101, 9, 2700, 4, A19</t>
+          <t>KitchenAid® Dishwasher, PrintShield Series, 120 V, 15 A, Built-in Mounting, 44 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>PrintShield Series Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -3469,84 +3969,152 @@
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>Wattage</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PrintShield Series</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Color Temperature</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr"/>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>Base Type</t>
+          <t>Voltage Rating</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>A19</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW7" t="inlineStr"/>
       <c r="BX7" t="inlineStr"/>
-      <c r="BY7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ7" t="inlineStr"/>
       <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC7" t="inlineStr"/>
       <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr"/>
-      <c r="CH7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI7" t="inlineStr"/>
       <c r="CJ7" t="inlineStr"/>
-      <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" t="inlineStr"/>
-      <c r="CN7" t="inlineStr"/>
-      <c r="CO7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP7" t="inlineStr"/>
-      <c r="CQ7" t="inlineStr"/>
-      <c r="CR7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="inlineStr"/>
       <c r="CW7" t="inlineStr"/>
@@ -3718,22 +4286,30 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lighting</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K8" t="n">
         <v>1515806</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LB-1102</t>
+          <t>GDF650SSVSS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A19 LED BULB 9 WATT 2700K DIM</t>
+          <t>GDF650SSVSS GE Front Control Dishwasher 51 dBA 120V 15A Stainless Steel</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -3753,54 +4329,54 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Signify North America</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>LB-1102</t>
+          <t>GDF650SSVSS</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Lighting, LB-1102</t>
+          <t>GE, Dishwasher, GDF650SSVSS, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>LIGHTING LB-1102 9 WATTAGE 2700 COLOR TE</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 51DBA</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review LB-1102 Lighting, 9</t>
+          <t>GE® GDF650SSVSS Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Lighting, LB-1102, 9, 2700, A19</t>
+          <t>GE® Dishwasher, 120 V, 15 A, Built-in Mounting, 51 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -3831,76 +4407,148 @@
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>Wattage</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Color Temperature</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>Base Type</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW8" t="inlineStr"/>
       <c r="BX8" t="inlineStr"/>
-      <c r="BY8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ8" t="inlineStr"/>
       <c r="CA8" t="inlineStr"/>
-      <c r="CB8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC8" t="inlineStr"/>
       <c r="CD8" t="inlineStr"/>
-      <c r="CE8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr"/>
-      <c r="CH8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI8" t="inlineStr"/>
       <c r="CJ8" t="inlineStr"/>
-      <c r="CK8" t="inlineStr"/>
-      <c r="CL8" t="inlineStr"/>
-      <c r="CM8" t="inlineStr"/>
-      <c r="CN8" t="inlineStr"/>
-      <c r="CO8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP8" t="inlineStr"/>
-      <c r="CQ8" t="inlineStr"/>
-      <c r="CR8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU8" t="inlineStr"/>
       <c r="CV8" t="inlineStr"/>
       <c r="CW8" t="inlineStr"/>
@@ -4072,22 +4720,30 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lighting</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K9" t="n">
         <v>1515807</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LB-1103</t>
+          <t>FFID2426TS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A-19 LED 800LM SOFT WHITE</t>
+          <t>FFID2426TS Frigidaire Built-In Dishwasher 54 dBA 120V 15A Stainless Steel</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -4107,54 +4763,54 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Philips Lighting</t>
+          <t>Freud Inc (2435)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Rheem Manufacturing</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>FRIGIDAIRE®</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>LB-1103</t>
+          <t>FFID2426TS</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Lighting, LB-1103</t>
+          <t>Rheem Manufacturing FRIGIDAIRE, Dishwasher, Professional Series, FFID2426TS, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>LIGHTING LB-1103 800 LUMENS WHITE COLOR</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 54DBA</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review LB-1103 Lighting, White</t>
+          <t>FRIGIDAIRE® Professional Series FFID2426TS Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Lighting, LB-1103, 800, White</t>
+          <t>FRIGIDAIRE® Dishwasher, Professional Series, 120 V, 15 A, Built-in Mounting, 54 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Lighting, White</t>
+          <t>Professional Series Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -4185,68 +4841,152 @@
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>Lumens</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>Professional Series</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW9" t="inlineStr"/>
       <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ9" t="inlineStr"/>
       <c r="CA9" t="inlineStr"/>
-      <c r="CB9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC9" t="inlineStr"/>
       <c r="CD9" t="inlineStr"/>
-      <c r="CE9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr"/>
-      <c r="CH9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI9" t="inlineStr"/>
       <c r="CJ9" t="inlineStr"/>
-      <c r="CK9" t="inlineStr"/>
-      <c r="CL9" t="inlineStr"/>
-      <c r="CM9" t="inlineStr"/>
-      <c r="CN9" t="inlineStr"/>
-      <c r="CO9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP9" t="inlineStr"/>
-      <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="inlineStr"/>
       <c r="CW9" t="inlineStr"/>
@@ -4407,7 +5147,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.samsung.com/us/support/model/DW80CG5450SR/AA/</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -4418,22 +5162,30 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lighting</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K10" t="n">
         <v>1515808</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>LB-2201</t>
+          <t>DW80CG5450SR</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4FT LED FLAT PANEL 40W 4000K</t>
+          <t>DW80CG5450SR Samsung StormWash Dishwasher 42 dBA 120V 15A Stainless Steel</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -4453,54 +5205,54 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Signify NA</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>LB-2201</t>
+          <t>DW80CG5450SR</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Lighting, LB-2201</t>
+          <t>Samsung, Dishwasher, DW80CG5450SR, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>LIGHTING LB-2201 4 LENGTH 40 WATTAGE</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 42DBA</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review LB-2201 Lighting, 40</t>
+          <t>Samsung® DW80CG5450SR Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Lighting, LB-2201, 4, 40, 4000, 4</t>
+          <t>Samsung® Dishwasher, 120 V, 15 A, Built-in Mounting, 42 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -4531,84 +5283,148 @@
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Wattage</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>Color Temperature</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="inlineStr"/>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>Beam Distance</t>
+          <t>Voltage Rating</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW10" t="inlineStr"/>
       <c r="BX10" t="inlineStr"/>
-      <c r="BY10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ10" t="inlineStr"/>
       <c r="CA10" t="inlineStr"/>
-      <c r="CB10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC10" t="inlineStr"/>
       <c r="CD10" t="inlineStr"/>
-      <c r="CE10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr"/>
-      <c r="CH10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI10" t="inlineStr"/>
       <c r="CJ10" t="inlineStr"/>
-      <c r="CK10" t="inlineStr"/>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
-      <c r="CN10" t="inlineStr"/>
-      <c r="CO10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP10" t="inlineStr"/>
-      <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="inlineStr"/>
       <c r="CW10" t="inlineStr"/>
@@ -4780,22 +5596,30 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lighting</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K11" t="n">
         <v>1515809</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LB-2202</t>
+          <t>LDTS5551D</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>LED FLAT PANEL 2X4 40W</t>
+          <t>LDTS5551D LG Top Control Dishwasher QuadWash 46 dBA 120V 15A Stainless Steel</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -4815,54 +5639,54 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Signify North America</t>
+          <t>MSC Industrial Supply</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>LB-2202</t>
+          <t>LDTS5551D</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Lighting, LB-2202</t>
+          <t>LG, Dishwasher, Quadwash, LDTS5551D, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>LIGHTING LB-2202 40 WATTAGE</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 46DBA</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review LB-2202 Lighting, 40</t>
+          <t>LG® Quadwash LDTS5551D Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Lighting, LB-2202, 40</t>
+          <t>LG® Dishwasher, Quadwash, 120 V, 15 A, Built-in Mounting, 46 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Quadwash Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -4893,60 +5717,152 @@
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>Wattage</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Quadwash</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr"/>
-      <c r="BR11" t="inlineStr"/>
-      <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW11" t="inlineStr"/>
       <c r="BX11" t="inlineStr"/>
-      <c r="BY11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ11" t="inlineStr"/>
       <c r="CA11" t="inlineStr"/>
-      <c r="CB11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC11" t="inlineStr"/>
       <c r="CD11" t="inlineStr"/>
-      <c r="CE11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF11" t="inlineStr"/>
       <c r="CG11" t="inlineStr"/>
-      <c r="CH11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI11" t="inlineStr"/>
       <c r="CJ11" t="inlineStr"/>
-      <c r="CK11" t="inlineStr"/>
-      <c r="CL11" t="inlineStr"/>
-      <c r="CM11" t="inlineStr"/>
-      <c r="CN11" t="inlineStr"/>
-      <c r="CO11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP11" t="inlineStr"/>
-      <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="inlineStr"/>
@@ -5107,7 +6023,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.bosch-home.com/us/en/product/SHEM63W55N</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -5118,22 +6038,30 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K12" t="n">
         <v>1515810</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FA-6601</t>
+          <t>SHEM63W55N</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1/4-20 X 1IN HEX CAP SCR ZN GR5</t>
+          <t>SHEM63W55N Bosch 300 Series Dishwasher 46 dBA 120V 12A White</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -5153,54 +6081,54 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>BSH Home Appliances</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>FA-6601</t>
+          <t>SHEM63W55N</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, FA-6601</t>
+          <t>Bosch, Dishwasher, 300 Series, SHEM63W55N, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED FA-6601</t>
+          <t>DISHWASHER BLTLN PLS 120V 12A 46DBA</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review FA-6601 Uncategorized</t>
+          <t>Bosch® 300 Series SHEM63W55N Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, FA-6601</t>
+          <t>Bosch® Dishwasher, 300 Series, 120 V, 12 A, Built-in Mounting, 46 dBA Sound Level</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>300 Series Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -5231,52 +6159,144 @@
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>300 Series</t>
+        </is>
+      </c>
       <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
-      <c r="BQ12" t="inlineStr"/>
-      <c r="BR12" t="inlineStr"/>
-      <c r="BS12" t="inlineStr"/>
-      <c r="BT12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU12" t="inlineStr"/>
-      <c r="BV12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW12" t="inlineStr"/>
       <c r="BX12" t="inlineStr"/>
-      <c r="BY12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ12" t="inlineStr"/>
       <c r="CA12" t="inlineStr"/>
-      <c r="CB12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC12" t="inlineStr"/>
       <c r="CD12" t="inlineStr"/>
-      <c r="CE12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF12" t="inlineStr"/>
       <c r="CG12" t="inlineStr"/>
-      <c r="CH12" t="inlineStr"/>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI12" t="inlineStr"/>
       <c r="CJ12" t="inlineStr"/>
-      <c r="CK12" t="inlineStr"/>
-      <c r="CL12" t="inlineStr"/>
-      <c r="CM12" t="inlineStr"/>
-      <c r="CN12" t="inlineStr"/>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
       <c r="CO12" t="inlineStr"/>
       <c r="CP12" t="inlineStr"/>
-      <c r="CQ12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr"/>
@@ -5448,22 +6468,30 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K13" t="n">
         <v>1515811</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FA-6602</t>
+          <t>KDPE234GPS</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1/4-20X1 HHCS ZINC GRADE 5</t>
+          <t>KDPE234GPS KitchenAid 39 dBA Dishwasher FreeFlex Stainless Steel</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -5483,54 +6511,54 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fastenal Co</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Whirlpool Corporation</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>KitchenAid</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>FA-6602</t>
+          <t>KDPE234GPS</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, FA-6602</t>
+          <t>KitchenAid, Dishwasher, PrintShield Series, KDPE234GPS, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED FA-6602</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 39DBA</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review FA-6602 Uncategorized</t>
+          <t>KitchenAid® PrintShield Series KDPE234GPS Dishwasher, Built-in Mounting, Stainless Steel</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, FA-6602</t>
+          <t>KitchenAid® Dishwasher, PrintShield Series, 120 V, 15 A, Built-in Mounting, 39 dBA Sound Level, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>PrintShield Series Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -5561,52 +6589,152 @@
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>PrintShield Series</t>
+        </is>
+      </c>
       <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
-      <c r="BQ13" t="inlineStr"/>
-      <c r="BR13" t="inlineStr"/>
-      <c r="BS13" t="inlineStr"/>
-      <c r="BT13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW13" t="inlineStr"/>
       <c r="BX13" t="inlineStr"/>
-      <c r="BY13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ13" t="inlineStr"/>
       <c r="CA13" t="inlineStr"/>
-      <c r="CB13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC13" t="inlineStr"/>
       <c r="CD13" t="inlineStr"/>
-      <c r="CE13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF13" t="inlineStr"/>
       <c r="CG13" t="inlineStr"/>
-      <c r="CH13" t="inlineStr"/>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI13" t="inlineStr"/>
       <c r="CJ13" t="inlineStr"/>
-      <c r="CK13" t="inlineStr"/>
-      <c r="CL13" t="inlineStr"/>
-      <c r="CM13" t="inlineStr"/>
-      <c r="CN13" t="inlineStr"/>
-      <c r="CO13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO13" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP13" t="inlineStr"/>
-      <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="inlineStr"/>
       <c r="CW13" t="inlineStr"/>
@@ -5778,22 +6906,30 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fasteners</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K14" t="n">
         <v>1515812</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FA-7701</t>
+          <t>G7106SCVi</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16D COMMON NAIL 3-1/2IN 5LB BOX</t>
+          <t>G7106SCVi Miele Fully Integrated Dishwasher 42 dBA 120V 15A Panel Ready</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -5813,54 +6949,54 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Grip-Rite</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Miele Inc.</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Miele</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>FA-7701</t>
+          <t>G7106SCVi</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Fasteners</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Fasteners, FA-77015</t>
+          <t>Miele, Dishwasher, G7106SCVi, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>FASTENERS FA-7701 5 SIZE</t>
+          <t>DISHWASHER BLTLN PLS 120V 15A 42DBA</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review FA-7701 Fasteners, 5</t>
+          <t>Miele® G7106SCVi Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Fasteners, FA-7701, 5</t>
+          <t>Miele® Dishwasher, 120 V, 15 A, Built-in Mounting, 42 dBA Sound Level</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Fasteners, 5</t>
+          <t>Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -5891,60 +7027,140 @@
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr"/>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="inlineStr"/>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW14" t="inlineStr"/>
       <c r="BX14" t="inlineStr"/>
-      <c r="BY14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ14" t="inlineStr"/>
       <c r="CA14" t="inlineStr"/>
-      <c r="CB14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC14" t="inlineStr"/>
       <c r="CD14" t="inlineStr"/>
-      <c r="CE14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF14" t="inlineStr"/>
       <c r="CG14" t="inlineStr"/>
-      <c r="CH14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI14" t="inlineStr"/>
       <c r="CJ14" t="inlineStr"/>
-      <c r="CK14" t="inlineStr"/>
-      <c r="CL14" t="inlineStr"/>
-      <c r="CM14" t="inlineStr"/>
-      <c r="CN14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="CM14" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN14" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
       <c r="CO14" t="inlineStr"/>
       <c r="CP14" t="inlineStr"/>
-      <c r="CQ14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
-      <c r="CT14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="inlineStr"/>
@@ -6116,22 +7332,30 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fasteners</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K15" t="n">
         <v>1515813</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FA-7702</t>
+          <t>WDF520PADM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3-1/2IN 16D NAIL BRIGHT</t>
+          <t>WDF520PADM Whirlpool Front Control Dishwasher 55 dBA 120V 12A White</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -6151,54 +7375,54 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Grip Rite Inc</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Whirlpool Corporation</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>Whirlpool®</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>FA-7702</t>
+          <t>WDF520PADM</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Fasteners</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Fasteners, FA-7702</t>
+          <t>Whirlpool, Dishwasher, Eco Series, WDF520PADM, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>FASTENERS FA-7702</t>
+          <t>DISHWASHER BLTLN PLS 120V 12A 55DBA</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review FA-7702 Fasteners</t>
+          <t>Whirlpool® Eco Series WDF520PADM Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Fasteners, FA-7702</t>
+          <t>Whirlpool® Dishwasher, Eco Series, 120 V, 12 A, Built-in Mounting, 55 dBA Sound Level</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Fasteners</t>
+          <t>Eco Series Dishwasher, Built-in Mounting</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -6229,52 +7453,144 @@
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
+          <t>Dishwashers</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>Eco Series</t>
+        </is>
+      </c>
       <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="inlineStr"/>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr"/>
-      <c r="BR15" t="inlineStr"/>
-      <c r="BS15" t="inlineStr"/>
-      <c r="BT15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU15" t="inlineStr"/>
-      <c r="BV15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW15" t="inlineStr"/>
       <c r="BX15" t="inlineStr"/>
-      <c r="BY15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ15" t="inlineStr"/>
       <c r="CA15" t="inlineStr"/>
-      <c r="CB15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC15" t="inlineStr"/>
       <c r="CD15" t="inlineStr"/>
-      <c r="CE15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF15" t="inlineStr"/>
       <c r="CG15" t="inlineStr"/>
-      <c r="CH15" t="inlineStr"/>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI15" t="inlineStr"/>
       <c r="CJ15" t="inlineStr"/>
-      <c r="CK15" t="inlineStr"/>
-      <c r="CL15" t="inlineStr"/>
-      <c r="CM15" t="inlineStr"/>
-      <c r="CN15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN15" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
       <c r="CO15" t="inlineStr"/>
       <c r="CP15" t="inlineStr"/>
-      <c r="CQ15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="inlineStr"/>
-      <c r="CT15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="inlineStr"/>
       <c r="CW15" t="inlineStr"/>
@@ -6446,22 +7762,30 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Large Appliances</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dishwashers</t>
+        </is>
+      </c>
       <c r="K16" t="n">
         <v>1515814</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>EL-8801</t>
+          <t>PDT785SBNTS</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>12/2 NM-B ROMEX 250FT</t>
+          <t>PDT785SBNTS GE Profile Dishwasher 47 dBA 120V 15A Black Stainless Steel</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -6481,54 +7805,54 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Southwire Company</t>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review</t>
+          <t>GE Profile</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>EL-8801</t>
+          <t>PDT785SBNTS</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Electrical, EL-8801</t>
+          <t>GE Profile, Dishwasher, Profile Series, PDT785SBNTS, Built-in Mounting</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>ELECTRICAL EL-8801 250 LENGTH 250 BEAM D</t>
+          <t>DISHWASHER BLTLN SST SST 120V 15A 47DBA</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review EL-8801 Electrical</t>
+          <t>GE Profile® Profile Series PDT785SBNTS Dishwasher, Built-in Mounting, Black Stainless Steel</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Electrical, EL-8801, 250, 250</t>
+          <t>GE Profile® Dishwasher, Profile Series, 120 V, 15 A, Built-in Mounting, 47 dBA Sound Level, Black Stainless Steel, Black Stainless Steel</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Profile Series Dishwasher, Built-in Mounting, Black Stainless Steel, Black Stainless Steel</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -6559,68 +7883,152 @@
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Dishwashers</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>Profile Series</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr"/>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Beam Distance</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>Number of Wash Cycles</t>
+        </is>
+      </c>
       <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="inlineStr"/>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr"/>
-      <c r="BR16" t="inlineStr"/>
-      <c r="BS16" t="inlineStr"/>
-      <c r="BT16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>Voltage Rating</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>Amperage Rating</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>Mounting Type</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>Built-in</t>
+        </is>
+      </c>
       <c r="BU16" t="inlineStr"/>
-      <c r="BV16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>Plug Type</t>
+        </is>
+      </c>
       <c r="BW16" t="inlineStr"/>
       <c r="BX16" t="inlineStr"/>
-      <c r="BY16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
       <c r="BZ16" t="inlineStr"/>
       <c r="CA16" t="inlineStr"/>
-      <c r="CB16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>Depth With Door Open</t>
+        </is>
+      </c>
       <c r="CC16" t="inlineStr"/>
       <c r="CD16" t="inlineStr"/>
-      <c r="CE16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>Minimum Height</t>
+        </is>
+      </c>
       <c r="CF16" t="inlineStr"/>
       <c r="CG16" t="inlineStr"/>
-      <c r="CH16" t="inlineStr"/>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>Maximum Height</t>
+        </is>
+      </c>
       <c r="CI16" t="inlineStr"/>
       <c r="CJ16" t="inlineStr"/>
-      <c r="CK16" t="inlineStr"/>
-      <c r="CL16" t="inlineStr"/>
-      <c r="CM16" t="inlineStr"/>
-      <c r="CN16" t="inlineStr"/>
-      <c r="CO16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr">
+        <is>
+          <t>Sound Level</t>
+        </is>
+      </c>
+      <c r="CL16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="CM16" t="inlineStr">
+        <is>
+          <t>dBA</t>
+        </is>
+      </c>
+      <c r="CN16" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="CO16" t="inlineStr">
+        <is>
+          <t>Black Stainless Steel</t>
+        </is>
+      </c>
       <c r="CP16" t="inlineStr"/>
-      <c r="CQ16" t="inlineStr"/>
-      <c r="CR16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>Black Stainless Steel</t>
+        </is>
+      </c>
       <c r="CS16" t="inlineStr"/>
-      <c r="CT16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
       <c r="CU16" t="inlineStr"/>
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="inlineStr"/>
@@ -6792,7 +8200,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -6802,12 +8210,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EL-8802</t>
+          <t>3MABR-7100033445</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>12-2 W/G ROMEX WIRE 250'</t>
+          <t>3M 775L Stikit Film P100 - Cubitron II 50 Disc/Box</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -6827,7 +8235,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Southwire Co.</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -6843,38 +8251,38 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>EL-8802</t>
+          <t>3MABR-7100033445</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Electrical, EL-8802</t>
+          <t>UNRESOLVED — needs manual review, Uncategorized, 3MABR-7100033445</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>ELECTRICAL EL-8802 250 LENGTH 2 WATTAGE</t>
+          <t>UNCATEGORIZED 3MABR-7100033445</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review EL-8802 Electrical, 2</t>
+          <t>UNRESOLVED — needs manual review 3MABR-7100033445 Uncategorized</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Electrical, EL-8802, 250, 2</t>
+          <t>UNRESOLVED — needs manual review Uncategorized, 3MABR-7100033445</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -6908,27 +8316,11 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>Wattage</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr"/>
       <c r="BJ17" t="inlineStr"/>
       <c r="BK17" t="inlineStr"/>
@@ -7138,7 +8530,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -7148,12 +8540,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>EL-9901</t>
+          <t>3MABR-7100077889</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>GFCI OUTLET 20A 125V TR WHT</t>
+          <t>3M Trizact Cloth Belt P220 - 3x24 In 10pc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -7173,7 +8565,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Leviton Mfg</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7189,38 +8581,38 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>EL-9901</t>
+          <t>3MABR-7100077889</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Electrical, EL-9901</t>
+          <t>UNRESOLVED — needs manual review, Uncategorized, 3MABR-7100077889</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>ELECTRICAL EL-9901 125 VOLTAGE 20 AMPERA</t>
+          <t>UNCATEGORIZED 3MABR-7100077889 10 QUANTI</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review EL-9901 Electrical, White, 125</t>
+          <t>UNRESOLVED — needs manual review 3MABR-7100077889 Uncategorized</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Electrical, EL-9901, 125, 20, White</t>
+          <t>UNRESOLVED — needs manual review Uncategorized, 3MABR-7100077889, 10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Electrical, White</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -7256,36 +8648,20 @@
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>Amperage</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr"/>
       <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="inlineStr"/>
@@ -7492,7 +8868,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7502,12 +8878,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>EL-9902</t>
+          <t>LEDPAR30-8811</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>20AMP GFCI RECEPT TAMPER RESIST</t>
+          <t>LED PAR30 Short Neck Flood Light Bulb 11W 4000K</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -7527,7 +8903,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Leviton</t>
+          <t>Freud Inc (2435)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -7543,38 +8919,38 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>EL-9902</t>
+          <t>LEDPAR30-8811</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, EL-9902</t>
+          <t>UNRESOLVED — needs manual review, Lighting, LEDPAR30-8811</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED EL-9902 20 AMPERAGE</t>
+          <t>LIGHTING LEDPAR30-8811 11 WATTAGE 4000 C</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review EL-9902 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review LEDPAR30-8811 Lighting, 11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, EL-9902, 20</t>
+          <t>UNRESOLVED — needs manual review Lighting, LEDPAR30-8811, 11, 4000</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -7610,17 +8986,25 @@
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>Amperage</t>
+          <t>Wattage</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Color Temperature</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr"/>
       <c r="BK19" t="inlineStr"/>
@@ -7830,7 +9214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -7840,12 +9224,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>EL-9903</t>
+          <t>LEDA19-7722</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>DECORA ROCKER SWITCH 15A WHT</t>
+          <t>LED A19 General Purpose Bulb 9W 2700K Dimmable</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -7865,7 +9249,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Leviton Manufacturing</t>
+          <t>Freud Inc (2435)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -7881,38 +9265,38 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>EL-9903</t>
+          <t>LEDA19-7722</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Electrical, EL-9903</t>
+          <t>UNRESOLVED — needs manual review, Lighting, LEDA19-7722</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>ELECTRICAL EL-9903 15 AMPERAGE WHITE COL</t>
+          <t>LIGHTING LEDA19-7722 9 WATTAGE 2700 COLO</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review EL-9903 Electrical, White</t>
+          <t>UNRESOLVED — needs manual review LEDA19-7722 Lighting, 9</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Electrical, EL-9903, 15, White</t>
+          <t>UNRESOLVED — needs manual review Lighting, LEDA19-7722, 9, 2700, A19</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Electrical, White</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -7948,28 +9332,36 @@
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>Amperage</t>
+          <t>Wattage</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Color Temperature</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr"/>
-      <c r="BJ20" t="inlineStr"/>
-      <c r="BK20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>Base Type</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
       <c r="BL20" t="inlineStr"/>
       <c r="BM20" t="inlineStr"/>
       <c r="BN20" t="inlineStr"/>
@@ -8176,7 +9568,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Hand Tools</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -8186,12 +9578,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>HV-1001</t>
+          <t>HTOOL-88231</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16X25X1 MERV11 PLEATED FILTER</t>
+          <t>Adjustable Wrench 10 Inch Chrome Vanadium Steel</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -8211,7 +9603,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Honeywell Intl</t>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8227,38 +9619,38 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>HV-1001</t>
+          <t>HTOOL-88231</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Hand Tools</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, HV-100116</t>
+          <t>UNRESOLVED — needs manual review, Hand Tools, HTOOL-88231</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED HV-1001 16 SIZE</t>
+          <t>HAND TOOLS HTOOL-88231 STEEL MATERIAL CH</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review HV-1001 Uncategorized, 16</t>
+          <t>UNRESOLVED — needs manual review HTOOL-88231 Hand Tools, Steel, Chrome</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, HV-1001, 16</t>
+          <t>UNRESOLVED — needs manual review Hand Tools, HTOOL-88231, Steel, Chrome</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Uncategorized, 16</t>
+          <t>Hand Tools, Steel, Chrome</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -8294,17 +9686,25 @@
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr"/>
-      <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>Chrome</t>
+        </is>
+      </c>
       <c r="BI21" t="inlineStr"/>
       <c r="BJ21" t="inlineStr"/>
       <c r="BK21" t="inlineStr"/>
@@ -8514,7 +9914,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Hand Tools</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -8524,12 +9924,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>HV-1002</t>
+          <t>HTOOL-88232</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PLEATED AIR FILTR 16X25X1 M11</t>
+          <t>Claw Hammer 16oz Fiberglass Handle</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -8549,7 +9949,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Honeywell International</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8565,38 +9965,38 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>HV-1002</t>
+          <t>HTOOL-88232</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Hand Tools</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, HV-100216</t>
+          <t>UNRESOLVED — needs manual review, Hand Tools, HTOOL-8823216</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED HV-1002 16 SIZE</t>
+          <t>HAND TOOLS HTOOL-88232 16 SIZE</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review HV-1002 Uncategorized, 16</t>
+          <t>UNRESOLVED — needs manual review HTOOL-88232 Hand Tools, 16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, HV-1002, 16</t>
+          <t>UNRESOLVED — needs manual review Hand Tools, HTOOL-88232, 16</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Uncategorized, 16</t>
+          <t>Hand Tools, 16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -8852,7 +10252,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Power Tools</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -8862,12 +10262,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SF-2001</t>
+          <t>PTOOL-77401</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SAFETY GLASSES CLR ANTI-FOG ANSI</t>
+          <t>Cordless Impact Driver 18V Kit with Battery and Charger</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -8887,7 +10287,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3M Company</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8903,38 +10303,38 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SF-2001</t>
+          <t>PTOOL-77401</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Power Tools</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, SF-2001</t>
+          <t>UNRESOLVED — needs manual review, Power Tools, PTOOL-77401</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED SF-2001</t>
+          <t>POWER TOOLS PTOOL-77401 18 VOLTAGE</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review SF-2001 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review PTOOL-77401 Power Tools, 18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, SF-2001</t>
+          <t>UNRESOLVED — needs manual review Power Tools, PTOOL-77401, 18</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Power Tools</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -8968,8 +10368,16 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>Voltage</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="BF23" t="inlineStr"/>
       <c r="BG23" t="inlineStr"/>
       <c r="BH23" t="inlineStr"/>
@@ -9182,7 +10590,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -9192,12 +10600,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>SF-2002</t>
+          <t>PTOOL-77402</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>ANSI Z87.1 CLEAR SAFETY GLASSES</t>
+          <t>Angle Grinder 4.5 Inch Corded 7.5 Amp</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -9217,7 +10625,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3M Co.</t>
+          <t>MSC Industrial Supply</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -9233,38 +10641,38 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SF-2002</t>
+          <t>PTOOL-77402</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, SF-2002</t>
+          <t>UNRESOLVED — needs manual review, Abrasives, PTOOL-77402</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED SF-2002</t>
+          <t>ABRASIVES PTOOL-77402 7.5 AMPERAGE</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review SF-2002 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review PTOOL-77402 Abrasives</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, SF-2002</t>
+          <t>UNRESOLVED — needs manual review Abrasives, PTOOL-77402, 7.5</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -9298,8 +10706,16 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>Amperage</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="BF24" t="inlineStr"/>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
@@ -9512,7 +10928,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -9522,12 +10938,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>SF-3001</t>
+          <t>ELEC-55501</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>NITRILE GLOVES PF LG 100CT</t>
+          <t>Wire Nuts Assorted Sizes 100pc Box</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -9547,7 +10963,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Ansell Ltd</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -9563,38 +10979,38 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>SF-3001</t>
+          <t>ELEC-55501</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, SF-3001</t>
+          <t>UNRESOLVED — needs manual review, Electrical, ELEC-55501</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED SF-3001</t>
+          <t>ELECTRICAL ELEC-55501 100 QUANTITY</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review SF-3001 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review ELEC-55501 Electrical</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, SF-3001</t>
+          <t>UNRESOLVED — needs manual review Electrical, ELEC-55501, 100</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -9628,8 +11044,16 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD25" t="inlineStr"/>
-      <c r="BE25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="BF25" t="inlineStr"/>
       <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="inlineStr"/>
@@ -9842,7 +11266,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Safety &amp; PPE</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -9852,12 +11276,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>SF-3002</t>
+          <t>ELEC-55502</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>DISP NITRILE GLOVE LARGE 100PK</t>
+          <t>GFCI Outlet 15A 125V Tamper Resistant White</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -9877,7 +11301,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Ansell Limited</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9893,38 +11317,38 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>SF-3002</t>
+          <t>ELEC-55502</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Safety &amp; PPE</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Safety &amp; PPE, SF-3002</t>
+          <t>UNRESOLVED — needs manual review, Electrical, ELEC-55502</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>SAFETY &amp; PPE SF-3002 100 QUANTITY</t>
+          <t>ELECTRICAL ELEC-55502 125 VOLTAGE 15 AMP</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review SF-3002 Safety &amp; PPE</t>
+          <t>UNRESOLVED — needs manual review ELEC-55502 Electrical, White, 125</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Safety &amp; PPE, SF-3002, 100</t>
+          <t>UNRESOLVED — needs manual review Electrical, ELEC-55502, 125, 15, White</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Safety &amp; PPE</t>
+          <t>Electrical, White</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -9960,20 +11384,36 @@
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>125</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr"/>
-      <c r="BG26" t="inlineStr"/>
-      <c r="BH26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>Amperage</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="BI26" t="inlineStr"/>
-      <c r="BJ26" t="inlineStr"/>
-      <c r="BK26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
       <c r="BL26" t="inlineStr"/>
       <c r="BM26" t="inlineStr"/>
       <c r="BN26" t="inlineStr"/>
@@ -10180,7 +11620,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -10190,12 +11630,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PT-4001</t>
+          <t>SAFE-33301</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>20V MAX CORDLESS DRILL DRIVER KIT</t>
+          <t>Safety Glasses Clear Anti-Fog Lens ANSI Z87.1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -10215,7 +11655,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>DEWALT Industrial</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -10231,38 +11671,38 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>PT-4001</t>
+          <t>SAFE-33301</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Power Tools, PT-4001</t>
+          <t>UNRESOLVED — needs manual review, Uncategorized, SAFE-33301</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>POWER TOOLS PT-4001 20 VOLTAGE</t>
+          <t>UNCATEGORIZED SAFE-33301</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review PT-4001 Power Tools, 20</t>
+          <t>UNRESOLVED — needs manual review SAFE-33301 Uncategorized</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Power Tools, PT-4001, 20</t>
+          <t>UNRESOLVED — needs manual review Uncategorized, SAFE-33301</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -10296,16 +11736,8 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD27" t="inlineStr">
-        <is>
-          <t>Voltage</t>
-        </is>
-      </c>
-      <c r="BE27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="inlineStr"/>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="inlineStr"/>
@@ -10518,7 +11950,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -10528,12 +11960,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PT-4002</t>
+          <t>SAFE-33302</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>DRILL DRIVER 20V KIT W/ BATTERY</t>
+          <t>Nitrile Disposable Gloves Powder Free Large 100ct</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -10553,7 +11985,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>DeWalt Ind. Tool</t>
+          <t>MSC Industrial Supply</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -10569,38 +12001,38 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>PT-4002</t>
+          <t>SAFE-33302</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Power Tools, PT-4002</t>
+          <t>UNRESOLVED — needs manual review, Uncategorized, SAFE-33302</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>POWER TOOLS PT-4002 20 VOLTAGE</t>
+          <t>UNCATEGORIZED SAFE-33302</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review PT-4002 Power Tools, 20</t>
+          <t>UNRESOLVED — needs manual review SAFE-33302 Uncategorized</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Power Tools, PT-4002, 20</t>
+          <t>UNRESOLVED — needs manual review Uncategorized, SAFE-33302</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -10634,16 +12066,8 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD28" t="inlineStr">
-        <is>
-          <t>Voltage</t>
-        </is>
-      </c>
-      <c r="BE28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
       <c r="BF28" t="inlineStr"/>
       <c r="BG28" t="inlineStr"/>
       <c r="BH28" t="inlineStr"/>
@@ -10856,7 +12280,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -10866,12 +12290,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PT-5001</t>
+          <t>HVAC-22201</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>7-1/4IN CIRC SAW 15A CORDED</t>
+          <t>Programmable Thermostat 7-Day Digital Display</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -10891,7 +12315,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Makita USA</t>
+          <t>Appliance Dealers Cooperative (APPDE)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -10907,38 +12331,38 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>PT-5001</t>
+          <t>HVAC-22201</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Hand Tools, PT-5001</t>
+          <t>UNRESOLVED — needs manual review, HVAC, HVAC-22201</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>HAND TOOLS PT-5001 15 AMPERAGE</t>
+          <t>HVAC HVAC-22201</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review PT-5001 Hand Tools</t>
+          <t>UNRESOLVED — needs manual review HVAC-22201 HVAC</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Hand Tools, PT-5001, 15</t>
+          <t>UNRESOLVED — needs manual review HVAC, HVAC-22201</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -10972,16 +12396,8 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD29" t="inlineStr">
-        <is>
-          <t>Amperage</t>
-        </is>
-      </c>
-      <c r="BE29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
       <c r="BF29" t="inlineStr"/>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
@@ -11194,7 +12610,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -11204,12 +12620,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PT-5002</t>
+          <t>HVAC-22202</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>CIRCULAR SAW 7.25IN 15AMP</t>
+          <t>Furnace Filter 16x25x1 MERV 11 Pleated</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -11229,7 +12645,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Makita U.S.A. Inc</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -11245,38 +12661,38 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>PT-5002</t>
+          <t>HVAC-22202</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Hand Tools, PT-5002</t>
+          <t>UNRESOLVED — needs manual review, HVAC, HVAC-2220216</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>HAND TOOLS PT-5002 15 AMPERAGE</t>
+          <t>HVAC HVAC-22202 16 SIZE</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review PT-5002 Hand Tools</t>
+          <t>UNRESOLVED — needs manual review HVAC-22202 HVAC, 16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Hand Tools, PT-5002, 15</t>
+          <t>UNRESOLVED — needs manual review HVAC, HVAC-22202, 16</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>HVAC, 16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -11312,12 +12728,12 @@
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>Amperage</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr"/>
@@ -11532,7 +12948,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -11542,12 +12958,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>HT-6001</t>
+          <t>PLUMB-11101</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10IN ADJ WRENCH CHROME VANADIUM</t>
+          <t>PVC Ball Valve 1 Inch Threaded</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -11567,7 +12983,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Klein Tools</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -11583,38 +12999,38 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>HT-6001</t>
+          <t>PLUMB-11101</t>
         </is>
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Hand Tools, HT-6001</t>
+          <t>UNRESOLVED — needs manual review, Plumbing, PLUMB-11101</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>HAND TOOLS HT-6001 CHROME COLOR</t>
+          <t>PLUMBING PLUMB-11101</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review HT-6001 Hand Tools, Chrome</t>
+          <t>UNRESOLVED — needs manual review PLUMB-11101 Plumbing</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Hand Tools, HT-6001, Chrome</t>
+          <t>UNRESOLVED — needs manual review Plumbing, PLUMB-11101</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Hand Tools, Chrome</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -11648,16 +13064,8 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD31" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="BE31" t="inlineStr">
-        <is>
-          <t>Chrome</t>
-        </is>
-      </c>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="inlineStr"/>
       <c r="BG31" t="inlineStr"/>
       <c r="BH31" t="inlineStr"/>
@@ -11870,7 +13278,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -11880,12 +13288,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>HT-6002</t>
+          <t>PLUMB-11102</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>ADJUSTABLE WRENCH 10IN CR-V</t>
+          <t>Braided Stainless Steel Supply Line 20 Inch</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -11905,7 +13313,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Klein Tools Inc</t>
+          <t>MSC Industrial Supply</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -11921,38 +13329,38 @@
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>HT-6002</t>
+          <t>PLUMB-11102</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Hand Tools, HT-6002</t>
+          <t>UNRESOLVED — needs manual review, Uncategorized, PLUMB-11102</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>HAND TOOLS HT-6002</t>
+          <t>UNCATEGORIZED PLUMB-11102 STAINLESS STEE</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review HT-6002 Hand Tools</t>
+          <t>UNRESOLVED — needs manual review PLUMB-11102 Uncategorized, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Hand Tools, HT-6002</t>
+          <t>UNRESOLVED — needs manual review Uncategorized, PLUMB-11102, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Hand Tools</t>
+          <t>Uncategorized, Stainless Steel, Stainless Steel</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -11986,11 +13394,27 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD32" t="inlineStr"/>
-      <c r="BE32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="BF32" t="inlineStr"/>
-      <c r="BG32" t="inlineStr"/>
-      <c r="BH32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>Stainless Steel</t>
+        </is>
+      </c>
       <c r="BI32" t="inlineStr"/>
       <c r="BJ32" t="inlineStr"/>
       <c r="BK32" t="inlineStr"/>
@@ -12200,7 +13624,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Fasteners</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -12210,12 +13634,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>LG-7001</t>
+          <t>FAST-99901</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>40V CORDLESS STRING TRIMMER</t>
+          <t>Hex Head Cap Screw 1/4-20 x 1 Inch Zinc 100pc</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -12235,7 +13659,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>EGO Power Plus</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -12251,38 +13675,38 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>LG-7001</t>
+          <t>FAST-99901</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Fasteners</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Power Tools, LG-7001</t>
+          <t>UNRESOLVED — needs manual review, Fasteners, FAST-99901</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>POWER TOOLS LG-7001 40 VOLTAGE</t>
+          <t>FASTENERS FAST-99901 100 QUANTITY</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review LG-7001 Power Tools, 40</t>
+          <t>UNRESOLVED — needs manual review FAST-99901 Fasteners</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Power Tools, LG-7001, 40</t>
+          <t>UNRESOLVED — needs manual review Fasteners, FAST-99901, 100</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Fasteners</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -12318,12 +13742,12 @@
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr"/>
@@ -12538,7 +13962,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Fasteners</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -12548,12 +13972,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>LG-7002</t>
+          <t>FAST-99902</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>STRING TRIMMER 40 VOLT CORDLESS</t>
+          <t>Self Tapping Sheet Metal Screw #8 x 1/2 In 200pc</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -12573,7 +13997,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>EGO Power+</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -12589,38 +14013,38 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>LG-7002</t>
+          <t>FAST-99902</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Fasteners</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Power Tools, LG-7002</t>
+          <t>UNRESOLVED — needs manual review, Fasteners, FAST-99902</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>POWER TOOLS LG-7002 40 VOLTAGE</t>
+          <t>FASTENERS FAST-99902 200 QUANTITY</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review LG-7002 Power Tools, 40</t>
+          <t>UNRESOLVED — needs manual review FAST-99902 Fasteners</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Power Tools, LG-7002, 40</t>
+          <t>UNRESOLVED — needs manual review Fasteners, FAST-99902, 200</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Power Tools</t>
+          <t>Fasteners</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -12656,12 +14080,12 @@
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>200</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr"/>
@@ -12876,7 +14300,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Adhesives &amp; Sealants</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -12886,12 +14310,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>AU-8001</t>
+          <t>ADH-66601</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>12V AGM BATTERY GRP 35 650CCA</t>
+          <t>Construction Adhesive Liquid Nails 10oz Tube</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -12911,7 +14335,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Interstate Batteries</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -12927,38 +14351,38 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>AU-8001</t>
+          <t>ADH-66601</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Adhesives &amp; Sealants</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, AU-8001</t>
+          <t>UNRESOLVED — needs manual review, Adhesives &amp; Sealants, ADH-6660110</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED AU-8001 12 VOLTAGE</t>
+          <t>ADHESIVES &amp; SEA ADH-66601 10 SIZE</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review AU-8001 Uncategorized, 12</t>
+          <t>UNRESOLVED — needs manual review ADH-66601 Adhesives &amp; Sealants, 10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, AU-8001, 12</t>
+          <t>UNRESOLVED — needs manual review Adhesives &amp; Sealants, ADH-66601, 10</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Adhesives &amp; Sealants, 10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -12994,12 +14418,12 @@
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr"/>
@@ -13214,7 +14638,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Adhesives &amp; Sealants</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -13224,12 +14648,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>AU-8002</t>
+          <t>ADH-66602</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>GRP35 AGM BATT 650 CCA</t>
+          <t>Silicone Sealant Clear 10.1oz Cartridge</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -13249,7 +14673,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Interstate Battery Sys</t>
+          <t>Grainger Industrial Supply</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -13265,38 +14689,38 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>AU-8002</t>
+          <t>ADH-66602</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Adhesives &amp; Sealants</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, AU-8002</t>
+          <t>UNRESOLVED — needs manual review, Adhesives &amp; Sealants, ADH-6660210.1</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED AU-8002</t>
+          <t>ADHESIVES &amp; SEA ADH-66602 10.1 SIZE</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review AU-8002 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review ADH-66602 Adhesives &amp; Sealants, 10.1</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, AU-8002</t>
+          <t>UNRESOLVED — needs manual review Adhesives &amp; Sealants, ADH-66602, 10.1</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Adhesives &amp; Sealants, 10.1</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -13330,8 +14754,16 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
       <c r="BF36" t="inlineStr"/>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
@@ -13544,7 +14976,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -13554,12 +14986,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BM-9001</t>
+          <t>LGHT-44401</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1/2IN OSB SUBFLR 4X8 SHEET</t>
+          <t>4ft LED Shop Light Fixture 4000K 40W</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -13579,7 +15011,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Freud Inc (2435)</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -13595,38 +15027,38 @@
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>BM-9001</t>
+          <t>LGHT-44401</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, BM-9001</t>
+          <t>UNRESOLVED — needs manual review, Lighting, LGHT-44401</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED BM-9001</t>
+          <t>LIGHTING LGHT-44401 4 LENGTH 40 WATTAGE</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review BM-9001 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review LGHT-44401 Lighting, 40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, BM-9001</t>
+          <t>UNRESOLVED — needs manual review Lighting, LGHT-44401, 4, 40, 4000, 4</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -13660,17 +15092,49 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD37" t="inlineStr"/>
-      <c r="BE37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="BF37" t="inlineStr"/>
-      <c r="BG37" t="inlineStr"/>
-      <c r="BH37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>Wattage</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="BI37" t="inlineStr"/>
-      <c r="BJ37" t="inlineStr"/>
-      <c r="BK37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>Color Temperature</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
       <c r="BL37" t="inlineStr"/>
-      <c r="BM37" t="inlineStr"/>
-      <c r="BN37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr">
+        <is>
+          <t>Beam Distance</t>
+        </is>
+      </c>
+      <c r="BN37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="BO37" t="inlineStr"/>
       <c r="BP37" t="inlineStr"/>
       <c r="BQ37" t="inlineStr"/>
@@ -13884,12 +15348,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BM-9002</t>
+          <t>LGHT-44402</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>OSB SHEATHING 1/2 IN 4X8</t>
+          <t>Motion Sensor Outdoor Wall Light Bronze Finish</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -13909,7 +15373,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Georgia Pacific Corp</t>
+          <t>Freud Inc (2435)</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -13925,7 +15389,7 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>BM-9002</t>
+          <t>LGHT-44402</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -13936,27 +15400,27 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, BM-9002</t>
+          <t>UNRESOLVED — needs manual review, Uncategorized, LGHT-44402</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED BM-9002</t>
+          <t>UNCATEGORIZED LGHT-44402 METAL ALLOY MAT</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review BM-9002 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review LGHT-44402 Uncategorized, Metal Alloy, Oil Rubbed Bronze</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, BM-9002</t>
+          <t>UNRESOLVED — needs manual review Uncategorized, LGHT-44402, Metal Alloy, Oil Rubbed Bronze</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Uncategorized, Metal Alloy, Oil Rubbed Bronze</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -13990,11 +15454,27 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD38" t="inlineStr"/>
-      <c r="BE38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>Metal Alloy</t>
+        </is>
+      </c>
       <c r="BF38" t="inlineStr"/>
-      <c r="BG38" t="inlineStr"/>
-      <c r="BH38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>Oil Rubbed Bronze</t>
+        </is>
+      </c>
       <c r="BI38" t="inlineStr"/>
       <c r="BJ38" t="inlineStr"/>
       <c r="BK38" t="inlineStr"/>
@@ -14204,7 +15684,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Janitorial &amp; Cleaning</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -14214,12 +15694,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>JN-1201</t>
+          <t>ABR-33305</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>MICROFIBER MOP PAD 18IN</t>
+          <t>Sanding Sponge Medium Grit 3pc Pack</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -14239,7 +15719,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Rubbermaid Comm</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -14255,38 +15735,38 @@
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>JN-1201</t>
+          <t>ABR-33305</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Janitorial &amp; Cleaning</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Janitorial &amp; Cleaning, JN-1201</t>
+          <t>UNRESOLVED — needs manual review, Abrasives, ABR-33305</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>JANITORIAL &amp; CL JN-1201</t>
+          <t>ABRASIVES ABR-33305 3 QUANTITY</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review JN-1201 Janitorial &amp; Cleaning</t>
+          <t>UNRESOLVED — needs manual review ABR-33305 Abrasives</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Janitorial &amp; Cleaning, JN-1201</t>
+          <t>UNRESOLVED — needs manual review Abrasives, ABR-33305, 3</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Janitorial &amp; Cleaning</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -14320,8 +15800,16 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD39" t="inlineStr"/>
-      <c r="BE39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="BF39" t="inlineStr"/>
       <c r="BG39" t="inlineStr"/>
       <c r="BH39" t="inlineStr"/>
@@ -14534,7 +16022,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janitorial &amp; Cleaning</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -14544,12 +16032,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JN-1202</t>
+          <t>ABR-33306</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>18IN MICROFIBER FLAT MOP</t>
+          <t>Wire Wheel Brush 4 Inch for Bench Grinder</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -14569,7 +16057,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Rubbermaid Commercial</t>
+          <t>Jam Industrial Supply LLC (JAMIN)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -14585,38 +16073,38 @@
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>JN-1202</t>
+          <t>ABR-33306</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Janitorial &amp; Cleaning</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Janitorial &amp; Cleaning, JN-1202</t>
+          <t>UNRESOLVED — needs manual review, Abrasives, ABR-33306</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>JANITORIAL &amp; CL JN-1202</t>
+          <t>ABRASIVES ABR-33306</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review JN-1202 Janitorial &amp; Cleaning</t>
+          <t>UNRESOLVED — needs manual review ABR-33306 Abrasives</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Janitorial &amp; Cleaning, JN-1202</t>
+          <t>UNRESOLVED — needs manual review Abrasives, ABR-33306</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Janitorial &amp; Cleaning</t>
+          <t>Abrasives</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -14864,30 +16352,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Appliances</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Large Appliances</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Dishwashers</t>
-        </is>
-      </c>
+          <t>Hand Tools</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
         <v>1515839</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>KDFM404KPS</t>
+          <t>HTOOL-88233</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>KDFM404KPS Dishwasher SS</t>
+          <t>Tape Measure 25ft Steel Blade Magnetic Tip</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -14923,38 +16403,38 @@
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>KDFM404KPS</t>
+          <t>HTOOL-88233</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Appliances &amp; Large Appliances &amp; Dishwashers</t>
+          <t>Hand Tools</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Dishwasher, KDFM404KPS, Built-in Mounting</t>
+          <t>UNRESOLVED — needs manual review, Hand Tools, HTOOL-88233</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>DISHWASHER BLTLN SST SST 120V 15A</t>
+          <t>HAND TOOLS HTOOL-88233 25 LENGTH 25 BEAM</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review® KDFM404KPS Dishwasher, Built-in Mounting, Stainless Steel</t>
+          <t>UNRESOLVED — needs manual review HTOOL-88233 Hand Tools, Steel</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review® Dishwasher, 120 V, 15 A, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>UNRESOLVED — needs manual review Hand Tools, HTOOL-88233, 25, 25, Steel</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Dishwasher, Built-in Mounting, Stainless Steel, Stainless Steel</t>
+          <t>Hand Tools, Steel</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -14985,140 +16465,76 @@
       <c r="BB41" t="inlineStr"/>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>Dishwashers</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>Series</t>
-        </is>
-      </c>
-      <c r="BE41" t="inlineStr"/>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="BF41" t="inlineStr"/>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="BH41" t="inlineStr"/>
+          <t>Beam Distance</t>
+        </is>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="BI41" t="inlineStr"/>
       <c r="BJ41" t="inlineStr">
         <is>
-          <t>Number of Wash Cycles</t>
-        </is>
-      </c>
-      <c r="BK41" t="inlineStr"/>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="BK41" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
       <c r="BL41" t="inlineStr"/>
-      <c r="BM41" t="inlineStr">
-        <is>
-          <t>Voltage Rating</t>
-        </is>
-      </c>
-      <c r="BN41" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="BO41" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="BP41" t="inlineStr">
-        <is>
-          <t>Amperage Rating</t>
-        </is>
-      </c>
-      <c r="BQ41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BR41" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BS41" t="inlineStr">
-        <is>
-          <t>Mounting Type</t>
-        </is>
-      </c>
-      <c r="BT41" t="inlineStr">
-        <is>
-          <t>Built-in</t>
-        </is>
-      </c>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
+      <c r="BO41" t="inlineStr"/>
+      <c r="BP41" t="inlineStr"/>
+      <c r="BQ41" t="inlineStr"/>
+      <c r="BR41" t="inlineStr"/>
+      <c r="BS41" t="inlineStr"/>
+      <c r="BT41" t="inlineStr"/>
       <c r="BU41" t="inlineStr"/>
-      <c r="BV41" t="inlineStr">
-        <is>
-          <t>Plug Type</t>
-        </is>
-      </c>
+      <c r="BV41" t="inlineStr"/>
       <c r="BW41" t="inlineStr"/>
       <c r="BX41" t="inlineStr"/>
-      <c r="BY41" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
+      <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="inlineStr"/>
       <c r="CA41" t="inlineStr"/>
-      <c r="CB41" t="inlineStr">
-        <is>
-          <t>Depth With Door Open</t>
-        </is>
-      </c>
+      <c r="CB41" t="inlineStr"/>
       <c r="CC41" t="inlineStr"/>
       <c r="CD41" t="inlineStr"/>
-      <c r="CE41" t="inlineStr">
-        <is>
-          <t>Minimum Height</t>
-        </is>
-      </c>
+      <c r="CE41" t="inlineStr"/>
       <c r="CF41" t="inlineStr"/>
       <c r="CG41" t="inlineStr"/>
-      <c r="CH41" t="inlineStr">
-        <is>
-          <t>Maximum Height</t>
-        </is>
-      </c>
+      <c r="CH41" t="inlineStr"/>
       <c r="CI41" t="inlineStr"/>
       <c r="CJ41" t="inlineStr"/>
-      <c r="CK41" t="inlineStr">
-        <is>
-          <t>Sound Level</t>
-        </is>
-      </c>
+      <c r="CK41" t="inlineStr"/>
       <c r="CL41" t="inlineStr"/>
       <c r="CM41" t="inlineStr"/>
-      <c r="CN41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="CO41" t="inlineStr">
-        <is>
-          <t>Stainless Steel</t>
-        </is>
-      </c>
+      <c r="CN41" t="inlineStr"/>
+      <c r="CO41" t="inlineStr"/>
       <c r="CP41" t="inlineStr"/>
-      <c r="CQ41" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="CR41" t="inlineStr">
-        <is>
-          <t>Stainless Steel</t>
-        </is>
-      </c>
+      <c r="CQ41" t="inlineStr"/>
+      <c r="CR41" t="inlineStr"/>
       <c r="CS41" t="inlineStr"/>
-      <c r="CT41" t="inlineStr">
-        <is>
-          <t>Additional Information</t>
-        </is>
-      </c>
+      <c r="CT41" t="inlineStr"/>
       <c r="CU41" t="inlineStr"/>
       <c r="CV41" t="inlineStr"/>
       <c r="CW41" t="inlineStr"/>
@@ -15290,7 +16706,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Hand Tools</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -15300,12 +16716,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>UNK-9999</t>
+          <t>PTOOL-77403</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Reciprocating Saw Corded 12 Amp with Blade</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -15325,7 +16741,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ABC Supply Co</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -15341,38 +16757,38 @@
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>UNK-9999</t>
+          <t>PTOOL-77403</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Hand Tools</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review, Uncategorized, UNK-9999</t>
+          <t>UNRESOLVED — needs manual review, Hand Tools, PTOOL-77403</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>UNCATEGORIZED UNK-9999</t>
+          <t>HAND TOOLS PTOOL-77403 12 AMPERAGE</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review UNK-9999 Uncategorized</t>
+          <t>UNRESOLVED — needs manual review PTOOL-77403 Hand Tools</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>UNRESOLVED — needs manual review Uncategorized, UNK-9999</t>
+          <t>UNRESOLVED — needs manual review Hand Tools, PTOOL-77403, 12</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Hand Tools</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -15406,8 +16822,16 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="BD42" t="inlineStr"/>
-      <c r="BE42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>Amperage</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="BF42" t="inlineStr"/>
       <c r="BG42" t="inlineStr"/>
       <c r="BH42" t="inlineStr"/>
